--- a/AAII_Financials/Quarterly/PASG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PASG_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="92">
   <si>
     <t>PASG</t>
   </si>
@@ -656,109 +656,112 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -825,8 +828,11 @@
       <c r="X8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -893,8 +899,11 @@
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -961,8 +970,11 @@
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -987,76 +999,80 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E12" s="3">
         <v>15100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>17300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>16800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>17700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>16900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>26800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>27700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>34000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>32100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>33100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>26500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>28900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>20800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>19900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>13100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>10000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>10400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>6800</v>
       </c>
-      <c r="V12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1123,17 +1139,20 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>5400</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1149,8 +1168,8 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1191,8 +1210,11 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1259,8 +1281,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1282,76 +1307,80 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>18400</v>
+      </c>
+      <c r="E17" s="3">
         <v>28700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>25400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>35900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>28200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>27500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>39800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>42800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>51200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>47100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>48500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>38900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>39100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>28600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>27300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>17900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>13600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>11600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>7800</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1359,67 +1388,70 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-28700</v>
+      </c>
+      <c r="F18" s="3">
         <v>-25400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-35900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-28200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-27500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-39800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-42800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-51200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-47100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-48500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-38900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-39100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-28600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-27300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-17900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-13600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-11600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-7800</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1444,8 +1476,9 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1453,31 +1486,31 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="F20" s="3">
         <v>1500</v>
       </c>
       <c r="G20" s="3">
+        <v>1500</v>
+      </c>
+      <c r="H20" s="3">
         <v>1200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>300</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>200</v>
-      </c>
-      <c r="M20" s="3">
-        <v>100</v>
       </c>
       <c r="N20" s="3">
         <v>100</v>
@@ -1492,28 +1525,31 @@
         <v>100</v>
       </c>
       <c r="R20" s="3">
+        <v>100</v>
+      </c>
+      <c r="S20" s="3">
         <v>300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-5700</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1521,67 +1557,70 @@
         <v>3</v>
       </c>
       <c r="E21" s="3">
+        <v>-26200</v>
+      </c>
+      <c r="F21" s="3">
         <v>-22900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-33400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-26100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-25800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-38600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-41900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-50500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-46500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-48200</v>
-      </c>
-      <c r="N21" s="3">
-        <v>-38700</v>
       </c>
       <c r="O21" s="3">
         <v>-38700</v>
       </c>
       <c r="P21" s="3">
+        <v>-38700</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-28300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-27000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-17500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-13100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-11300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-13400</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1648,76 +1687,82 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-16800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-27100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-23900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-34300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-27100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-26700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-39500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-42800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-51200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-46900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-48400</v>
-      </c>
-      <c r="N23" s="3">
-        <v>-38900</v>
       </c>
       <c r="O23" s="3">
         <v>-38900</v>
       </c>
       <c r="P23" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="Q23" s="3">
         <v>-28500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-27200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-17600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-13200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-11400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-13400</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1784,8 +1829,11 @@
       <c r="X24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1852,144 +1900,153 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-16800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-27100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-23900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-34300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-27100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-26700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-39500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-42800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-51200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-46900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-48400</v>
-      </c>
-      <c r="N26" s="3">
-        <v>-38900</v>
       </c>
       <c r="O26" s="3">
         <v>-38900</v>
       </c>
       <c r="P26" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="Q26" s="3">
         <v>-28500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-27200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-17600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-13200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-11400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-13400</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-16800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-27100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-23900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-34300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-27100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-26700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-39500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-42800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-51200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-46900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-48400</v>
-      </c>
-      <c r="N27" s="3">
-        <v>-38900</v>
       </c>
       <c r="O27" s="3">
         <v>-38900</v>
       </c>
       <c r="P27" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="Q27" s="3">
         <v>-28500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-27200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-17600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-13200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-11400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-13400</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2056,8 +2113,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2124,8 +2184,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2192,8 +2255,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2260,8 +2326,11 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2269,31 +2338,31 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
-        <v>-1500</v>
+        <v>-1600</v>
       </c>
       <c r="F32" s="3">
         <v>-1500</v>
       </c>
       <c r="G32" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="H32" s="3">
         <v>-1200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-300</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-200</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-100</v>
       </c>
       <c r="N32" s="3">
         <v>-100</v>
@@ -2308,96 +2377,102 @@
         <v>-100</v>
       </c>
       <c r="R32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S32" s="3">
         <v>-300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>5700</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-16800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-27100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-23900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-34300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-27100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-26700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-39500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-42800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-51200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-46900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-48400</v>
-      </c>
-      <c r="N33" s="3">
-        <v>-38900</v>
       </c>
       <c r="O33" s="3">
         <v>-38900</v>
       </c>
       <c r="P33" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="Q33" s="3">
         <v>-28500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-27200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-17600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-13200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-11400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-13400</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2464,149 +2539,158 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-16800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-27100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-23900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-34300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-27100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-26700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-39500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-42800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-51200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-46900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-48400</v>
-      </c>
-      <c r="N35" s="3">
-        <v>-38900</v>
       </c>
       <c r="O35" s="3">
         <v>-38900</v>
       </c>
       <c r="P35" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="Q35" s="3">
         <v>-28500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-27200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-17600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-13200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-11400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-13400</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2631,8 +2715,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2657,59 +2742,60 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>21700</v>
+      </c>
+      <c r="E41" s="3">
         <v>33600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>30300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>33400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>34600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>62600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>91100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>101600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>129000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>162900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>215500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>249500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>135000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>200600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>353400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>366800</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2725,53 +2811,56 @@
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>92600</v>
+      </c>
+      <c r="E42" s="3">
         <v>99200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>121200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>134400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>155000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>151200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>148100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>165500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>186800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>191500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>192300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>188100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>169800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>135100</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2787,14 +2876,17 @@
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W42" s="3">
-        <v>0</v>
+      <c r="W42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2861,8 +2953,11 @@
       <c r="X43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2929,59 +3024,62 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E45" s="3">
         <v>2900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>7400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>8800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>11300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>15900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>9300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>12100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>11000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>13400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>12400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>13800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>14800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>15300</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2997,59 +3095,62 @@
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>118000</v>
+      </c>
+      <c r="E46" s="3">
         <v>135700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>153600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>171600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>197000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>222500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>250600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>283000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>325100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>366500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>418800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>450900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>317200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>349500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>368200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>382100</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3065,8 +3166,11 @@
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3133,58 +3237,61 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>32200</v>
+      </c>
+      <c r="E48" s="3">
         <v>33100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>39600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>41200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>42200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>42800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>43600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>44500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>23800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>17800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>13500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>900</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>1100</v>
       </c>
       <c r="R48" s="3">
         <v>1100</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
+      <c r="S48" s="3">
+        <v>1100</v>
       </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
@@ -3201,8 +3308,11 @@
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3269,8 +3379,11 @@
       <c r="X49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3337,8 +3450,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3405,8 +3521,11 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3420,44 +3539,44 @@
         <v>400</v>
       </c>
       <c r="G52" s="3">
+        <v>400</v>
+      </c>
+      <c r="H52" s="3">
         <v>4300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>5200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>5700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>6200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>6700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>7200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>7600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>8000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>8300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>8800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>9200</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3473,8 +3592,11 @@
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3541,59 +3663,62 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>150500</v>
+      </c>
+      <c r="E54" s="3">
         <v>169300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>193700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>213200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>243500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>270100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>299400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>333200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>355100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>390900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>439500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>465200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>328000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>358700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>378100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>392400</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3609,8 +3734,11 @@
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3635,8 +3763,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3661,59 +3790,60 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E57" s="3">
         <v>2700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>8200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>9100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>9400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>9000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>16400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>6200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>7200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2500</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3729,8 +3859,11 @@
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3797,59 +3930,62 @@
       <c r="X58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E59" s="3">
         <v>17100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>16500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>14200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>14300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>17100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>18900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>18300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>20100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>13300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>14800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>13200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>15900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>15700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>6900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2700</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3865,59 +4001,62 @@
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E60" s="3">
         <v>19800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>19900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>17200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>18400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>21600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>27100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>27500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>29500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>22300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>31200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>19500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>21200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>19100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>14100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>5200</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3933,8 +4072,11 @@
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4001,59 +4143,62 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>22900</v>
+      </c>
+      <c r="E62" s="3">
         <v>23200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>23400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>25600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>23800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>24000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>24200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>24400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>6900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>6500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>6000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>4200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>500</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4069,8 +4214,11 @@
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4137,8 +4285,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4205,8 +4356,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4273,59 +4427,62 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>39300</v>
+      </c>
+      <c r="E66" s="3">
         <v>43000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>43300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>42900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>42200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>45700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>51400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>51900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>36400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>28700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>37300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>23700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>23300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>19800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>14700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5800</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4341,8 +4498,11 @@
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4367,8 +4527,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4435,8 +4596,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4503,8 +4667,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4571,8 +4738,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4639,59 +4809,62 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-594500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-577700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-550600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-526700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-492400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-465300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-438600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-399100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-356300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-305100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-258200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-209800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-170900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-132000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-103400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-76200</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4707,8 +4880,11 @@
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4775,8 +4951,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4843,8 +5022,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4911,59 +5093,62 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>111300</v>
+      </c>
+      <c r="E76" s="3">
         <v>126300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>150400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>170400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>201400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>224400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>248000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>281300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>318700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>362200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>402300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>441500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>304700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>338900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>363400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>386700</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4979,8 +5164,11 @@
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5047,149 +5235,158 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-16800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-27100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-23900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-34300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-27100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-26700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-39500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-42800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-51200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-46900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-48400</v>
-      </c>
-      <c r="N81" s="3">
-        <v>-38900</v>
       </c>
       <c r="O81" s="3">
         <v>-38900</v>
       </c>
       <c r="P81" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="Q81" s="3">
         <v>-28500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-27200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-17600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-13200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-11400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-13400</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5214,13 +5411,14 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="E83" s="3">
         <v>1000</v>
@@ -5229,7 +5427,7 @@
         <v>1000</v>
       </c>
       <c r="G83" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="H83" s="3">
         <v>900</v>
@@ -5241,29 +5439,29 @@
         <v>900</v>
       </c>
       <c r="K83" s="3">
+        <v>900</v>
+      </c>
+      <c r="L83" s="3">
         <v>700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>500</v>
-      </c>
-      <c r="M83" s="3">
-        <v>200</v>
       </c>
       <c r="N83" s="3">
         <v>200</v>
       </c>
       <c r="O83" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="P83" s="3">
         <v>300</v>
       </c>
       <c r="Q83" s="3">
+        <v>300</v>
+      </c>
+      <c r="R83" s="3">
         <v>200</v>
       </c>
-      <c r="R83" s="3">
-        <v>0</v>
-      </c>
       <c r="S83" s="3">
         <v>0</v>
       </c>
@@ -5273,8 +5471,8 @@
       <c r="U83" s="3">
         <v>0</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>3</v>
+      <c r="V83" s="3">
+        <v>0</v>
       </c>
       <c r="W83" s="3" t="s">
         <v>3</v>
@@ -5282,8 +5480,11 @@
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5350,8 +5551,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5418,8 +5622,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5486,8 +5693,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5554,8 +5764,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5622,76 +5835,82 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-19500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-19200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-17100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-22400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-24000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-23400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-26100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-44700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-30800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-41100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-24300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-30700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-29400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-17500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-11700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-21900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-17500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-11400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-10800</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5716,8 +5935,9 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5725,40 +5945,40 @@
         <v>0</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
       <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-7300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-11500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4000</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-800</v>
       </c>
       <c r="O91" s="3">
         <v>-800</v>
       </c>
       <c r="P91" s="3">
-        <v>-100</v>
+        <v>-800</v>
       </c>
       <c r="Q91" s="3">
         <v>-100</v>
@@ -5767,25 +5987,28 @@
         <v>-100</v>
       </c>
       <c r="S91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
         <v>-100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-200</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5852,8 +6075,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5920,76 +6146,82 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E94" s="3">
         <v>22500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>14000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>21200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-4800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>16000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>17300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-11600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-10300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-20400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-36500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-135400</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>-100</v>
       </c>
       <c r="R94" s="3">
         <v>-100</v>
       </c>
       <c r="S94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
         <v>-100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-700</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6014,8 +6246,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6082,8 +6315,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6150,8 +6386,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6218,8 +6457,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6286,8 +6528,11 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -6295,67 +6540,70 @@
         <v>0</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>100</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>-600</v>
-      </c>
-      <c r="H100" s="3">
-        <v>-400</v>
       </c>
       <c r="I100" s="3">
         <v>-400</v>
       </c>
       <c r="J100" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>500</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>165600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>400</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>-1600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>229900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>109900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>46300</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6422,72 +6670,78 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-11900</v>
+      </c>
+      <c r="E102" s="3">
         <v>3300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-3100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-28000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-28600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-10500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-27400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-33900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-52600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-34100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>114500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-65600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-152900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-13400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>208000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-18300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>98400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>34900</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PASG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PASG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="92">
   <si>
     <t>PASG</t>
   </si>
@@ -656,112 +656,116 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -831,8 +835,11 @@
       <c r="Y8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -902,8 +909,11 @@
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -973,8 +983,11 @@
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1000,79 +1013,83 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E12" s="3">
         <v>12200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>15100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>17300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>16800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>17700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>16900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>26800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>27700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>34000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>32100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>33100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>26500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>28900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>20800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>19900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>13100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>10000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>10400</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>6800</v>
       </c>
-      <c r="W12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1142,20 +1159,23 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>5400</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1171,8 +1191,8 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1213,8 +1233,11 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1284,8 +1307,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1308,79 +1334,83 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>18100</v>
+      </c>
+      <c r="E17" s="3">
         <v>18400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>28700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>25400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>35900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>28200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>27500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>39800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>42800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>51200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>47100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>48500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>38900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>39100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>28600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>27300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>17900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>13600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>11600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>7800</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1388,70 +1418,73 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-18400</v>
+      </c>
+      <c r="F18" s="3">
         <v>-28700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-25400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-35900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-28200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-27500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-39800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-42800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-51200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-47100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-48500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-38900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-39100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-28600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-27300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-17900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-13600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-11600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-7800</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1477,8 +1510,9 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1486,34 +1520,34 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F20" s="3">
         <v>1600</v>
-      </c>
-      <c r="F20" s="3">
-        <v>1500</v>
       </c>
       <c r="G20" s="3">
         <v>1500</v>
       </c>
       <c r="H20" s="3">
+        <v>1500</v>
+      </c>
+      <c r="I20" s="3">
         <v>1200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>300</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>200</v>
-      </c>
-      <c r="N20" s="3">
-        <v>100</v>
       </c>
       <c r="O20" s="3">
         <v>100</v>
@@ -1528,28 +1562,31 @@
         <v>100</v>
       </c>
       <c r="S20" s="3">
+        <v>100</v>
+      </c>
+      <c r="T20" s="3">
         <v>300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-5700</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1557,70 +1594,73 @@
         <v>3</v>
       </c>
       <c r="E21" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="F21" s="3">
         <v>-26200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-22900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-33400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-26100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-25800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-38600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-41900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-50500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-46500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-48200</v>
-      </c>
-      <c r="O21" s="3">
-        <v>-38700</v>
       </c>
       <c r="P21" s="3">
         <v>-38700</v>
       </c>
       <c r="Q21" s="3">
+        <v>-38700</v>
+      </c>
+      <c r="R21" s="3">
         <v>-28300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-27000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-17500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-13100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-11300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-13400</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1690,79 +1730,85 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-16700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-16800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-27100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-23900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-34300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-27100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-26700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-39500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-42800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-51200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-46900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-48400</v>
-      </c>
-      <c r="O23" s="3">
-        <v>-38900</v>
       </c>
       <c r="P23" s="3">
         <v>-38900</v>
       </c>
       <c r="Q23" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="R23" s="3">
         <v>-28500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-27200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-17600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-13200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-11400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-13400</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1832,8 +1878,11 @@
       <c r="Y24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1903,150 +1952,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-16700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-16800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-27100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-23900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-34300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-27100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-26700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-39500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-42800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-51200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-46900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-48400</v>
-      </c>
-      <c r="O26" s="3">
-        <v>-38900</v>
       </c>
       <c r="P26" s="3">
         <v>-38900</v>
       </c>
       <c r="Q26" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="R26" s="3">
         <v>-28500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-27200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-17600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-13200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-11400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-13400</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-16700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-16800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-27100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-23900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-34300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-27100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-26700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-39500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-42800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-51200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-46900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-48400</v>
-      </c>
-      <c r="O27" s="3">
-        <v>-38900</v>
       </c>
       <c r="P27" s="3">
         <v>-38900</v>
       </c>
       <c r="Q27" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="R27" s="3">
         <v>-28500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-27200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-17600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-13200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-11400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-13400</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2116,8 +2174,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2187,8 +2248,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2258,8 +2322,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2329,8 +2396,11 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2338,34 +2408,34 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F32" s="3">
         <v>-1600</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-1500</v>
       </c>
       <c r="G32" s="3">
         <v>-1500</v>
       </c>
       <c r="H32" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="I32" s="3">
         <v>-1200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-300</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-200</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-100</v>
       </c>
       <c r="O32" s="3">
         <v>-100</v>
@@ -2380,99 +2450,105 @@
         <v>-100</v>
       </c>
       <c r="S32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T32" s="3">
         <v>-300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>5700</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-16700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-16800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-27100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-23900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-34300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-27100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-26700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-39500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-42800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-51200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-46900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-48400</v>
-      </c>
-      <c r="O33" s="3">
-        <v>-38900</v>
       </c>
       <c r="P33" s="3">
         <v>-38900</v>
       </c>
       <c r="Q33" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="R33" s="3">
         <v>-28500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-27200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-17600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-13200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-11400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-13400</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2542,155 +2618,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-16700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-16800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-27100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-23900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-34300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-27100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-26700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-39500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-42800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-51200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-46900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-48400</v>
-      </c>
-      <c r="O35" s="3">
-        <v>-38900</v>
       </c>
       <c r="P35" s="3">
         <v>-38900</v>
       </c>
       <c r="Q35" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="R35" s="3">
         <v>-28500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-27200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-17600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-13200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-11400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-13400</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2716,8 +2801,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2743,62 +2829,63 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>36800</v>
+      </c>
+      <c r="E41" s="3">
         <v>21700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>33600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>30300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>33400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>34600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>62600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>91100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>101600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>129000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>162900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>215500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>249500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>135000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>200600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>353400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>366800</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2814,56 +2901,59 @@
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>67800</v>
+      </c>
+      <c r="E42" s="3">
         <v>92600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>99200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>121200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>134400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>155000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>151200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>148100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>165500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>186800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>191500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>192300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>188100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>169800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>135100</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2879,14 +2969,17 @@
       <c r="W42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X42" s="3">
-        <v>0</v>
+      <c r="X42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2956,8 +3049,11 @@
       <c r="Y43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3027,62 +3123,65 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E45" s="3">
         <v>3700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>7400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>8800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>11300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>15900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>9300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>12100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>11000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>13400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>12400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>13800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>14800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>15300</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3098,62 +3197,65 @@
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>108300</v>
+      </c>
+      <c r="E46" s="3">
         <v>118000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>135700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>153600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>171600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>197000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>222500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>250600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>283000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>325100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>366500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>418800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>450900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>317200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>349500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>368200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>382100</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3169,8 +3271,11 @@
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3240,61 +3345,64 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>31600</v>
+      </c>
+      <c r="E48" s="3">
         <v>32200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>33100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>39600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>41200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>42200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>42800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>43600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>44500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>23800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>17800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>13500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>900</v>
-      </c>
-      <c r="R48" s="3">
-        <v>1100</v>
       </c>
       <c r="S48" s="3">
         <v>1100</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
+      <c r="T48" s="3">
+        <v>1100</v>
       </c>
       <c r="U48" s="3" t="s">
         <v>3</v>
@@ -3311,8 +3419,11 @@
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3382,8 +3493,11 @@
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3453,8 +3567,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3524,13 +3641,16 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="E52" s="3">
         <v>400</v>
@@ -3542,44 +3662,44 @@
         <v>400</v>
       </c>
       <c r="H52" s="3">
+        <v>400</v>
+      </c>
+      <c r="I52" s="3">
         <v>4300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>5200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>6200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>6700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>7200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>7600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>8000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>8300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>8800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>9200</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3595,8 +3715,11 @@
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3666,62 +3789,65 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>140500</v>
+      </c>
+      <c r="E54" s="3">
         <v>150500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>169300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>193700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>213200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>243500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>270100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>299400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>333200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>355100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>390900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>439500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>465200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>328000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>358700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>378100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>392400</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3737,8 +3863,11 @@
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3764,8 +3893,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3791,62 +3921,63 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E57" s="3">
         <v>1300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>8200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>9100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>9400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>9000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>16400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>6200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>7200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2500</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3862,8 +3993,11 @@
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3933,62 +4067,65 @@
       <c r="Y58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E59" s="3">
         <v>15000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>17100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>16500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>14200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>14300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>17100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>18900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>18300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>20100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>13300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>14800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>13200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>15900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>15700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>6900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2700</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4004,62 +4141,65 @@
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>12800</v>
+      </c>
+      <c r="E60" s="3">
         <v>16300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>19800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>19900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>17200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>18400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>21600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>27100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>27500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>29500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>22300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>31200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>19500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>21200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>19100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>14100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>5200</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4075,8 +4215,11 @@
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4146,62 +4289,65 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>22800</v>
+      </c>
+      <c r="E62" s="3">
         <v>22900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>23200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>23400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>25600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>23800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>24000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>24200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>24400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>6900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>6500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>6000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>4200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>500</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4217,8 +4363,11 @@
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4288,8 +4437,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4359,8 +4511,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4430,62 +4585,65 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>35600</v>
+      </c>
+      <c r="E66" s="3">
         <v>39300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>43000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>43300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>42900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>42200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>45700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>51400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>51900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>36400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>28700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>37300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>23700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>23300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>19800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>14700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5800</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4501,8 +4659,11 @@
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4528,8 +4689,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4599,8 +4761,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4670,8 +4835,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4741,8 +4909,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4812,62 +4983,65 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-611200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-594500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-577700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-550600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-526700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-492400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-465300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-438600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-399100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-356300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-305100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-258200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-209800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-170900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-132000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-103400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-76200</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4883,8 +5057,11 @@
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4954,8 +5131,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5025,8 +5205,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5096,62 +5279,65 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>104900</v>
+      </c>
+      <c r="E76" s="3">
         <v>111300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>126300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>150400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>170400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>201400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>224400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>248000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>281300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>318700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>362200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>402300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>441500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>304700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>338900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>363400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>386700</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5167,8 +5353,11 @@
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5238,155 +5427,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-16700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-16800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-27100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-23900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-34300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-27100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-26700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-39500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-42800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-51200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-46900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-48400</v>
-      </c>
-      <c r="O81" s="3">
-        <v>-38900</v>
       </c>
       <c r="P81" s="3">
         <v>-38900</v>
       </c>
       <c r="Q81" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="R81" s="3">
         <v>-28500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-27200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-17600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-13200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-11400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-13400</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5412,8 +5610,9 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5421,7 +5620,7 @@
         <v>800</v>
       </c>
       <c r="E83" s="3">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="F83" s="3">
         <v>1000</v>
@@ -5430,7 +5629,7 @@
         <v>1000</v>
       </c>
       <c r="H83" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="I83" s="3">
         <v>900</v>
@@ -5442,29 +5641,29 @@
         <v>900</v>
       </c>
       <c r="L83" s="3">
+        <v>900</v>
+      </c>
+      <c r="M83" s="3">
         <v>700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>500</v>
-      </c>
-      <c r="N83" s="3">
-        <v>200</v>
       </c>
       <c r="O83" s="3">
         <v>200</v>
       </c>
       <c r="P83" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Q83" s="3">
         <v>300</v>
       </c>
       <c r="R83" s="3">
+        <v>300</v>
+      </c>
+      <c r="S83" s="3">
         <v>200</v>
       </c>
-      <c r="S83" s="3">
-        <v>0</v>
-      </c>
       <c r="T83" s="3">
         <v>0</v>
       </c>
@@ -5474,8 +5673,8 @@
       <c r="V83" s="3">
         <v>0</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>3</v>
+      <c r="W83" s="3">
+        <v>0</v>
       </c>
       <c r="X83" s="3" t="s">
         <v>3</v>
@@ -5483,8 +5682,11 @@
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5554,8 +5756,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5625,8 +5830,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5696,8 +5904,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5767,8 +5978,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5838,79 +6052,85 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-18900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-19500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-19200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-17100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-22400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-24000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-23400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-26100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-44700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-30800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-41100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-24300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-30700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-29400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-17500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-11700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-21900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-17500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-11400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-10800</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5936,8 +6156,9 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5963,25 +6184,25 @@
         <v>-800</v>
       </c>
       <c r="K91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="L91" s="3">
         <v>-2200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-7300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-11500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4000</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-800</v>
       </c>
       <c r="P91" s="3">
         <v>-800</v>
       </c>
       <c r="Q91" s="3">
-        <v>-100</v>
+        <v>-800</v>
       </c>
       <c r="R91" s="3">
         <v>-100</v>
@@ -5990,25 +6211,28 @@
         <v>-100</v>
       </c>
       <c r="T91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
         <v>-100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-200</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6078,8 +6302,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6149,79 +6376,85 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>25300</v>
+      </c>
+      <c r="E94" s="3">
         <v>7600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>22500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>14000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>21200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-4800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>16000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>17300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-11600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-10300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-20400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-36500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-135400</v>
-      </c>
-      <c r="R94" s="3">
-        <v>-100</v>
       </c>
       <c r="S94" s="3">
         <v>-100</v>
       </c>
       <c r="T94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
         <v>-100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-700</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6247,8 +6480,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6318,8 +6552,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6389,8 +6626,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6460,8 +6700,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6531,79 +6774,85 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>8700</v>
       </c>
       <c r="E100" s="3">
         <v>0</v>
       </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>100</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>-600</v>
-      </c>
-      <c r="I100" s="3">
-        <v>-400</v>
       </c>
       <c r="J100" s="3">
         <v>-400</v>
       </c>
       <c r="K100" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>500</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>165600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>400</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>-1600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>229900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>109900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>46300</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6673,75 +6922,81 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-11900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>3300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-3100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-28000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-28600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-10500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-27400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-33900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-52600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-34100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>114500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-65600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-152900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-13400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>208000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-18300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>98400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>34900</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PASG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PASG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="92">
   <si>
     <t>PASG</t>
   </si>
@@ -656,116 +656,120 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -838,8 +842,11 @@
       <c r="Z8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -912,8 +919,11 @@
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -986,8 +996,11 @@
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1014,82 +1027,86 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E12" s="3">
         <v>11500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>12200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>15100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>17300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>16800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>17700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>16900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>26800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>27700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>34000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>32100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>33100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>26500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>28900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>20800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>19900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>13100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>10000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>10400</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>6800</v>
       </c>
-      <c r="X12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1162,23 +1179,26 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
+      <c r="D14" s="3">
+        <v>400</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>5400</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1194,8 +1214,8 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1236,8 +1256,11 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1310,8 +1333,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1335,82 +1361,86 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>17400</v>
+      </c>
+      <c r="E17" s="3">
         <v>18100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>18400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>28700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>25400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>35900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>28200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>27500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>39800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>42800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>51200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>47100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>48500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>38900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>39100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>28600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>27300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>17900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>13600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>11600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>7800</v>
       </c>
-      <c r="X17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1418,73 +1448,76 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-18100</v>
+      </c>
+      <c r="F18" s="3">
         <v>-18400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-28700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-25400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-35900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-28200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-27500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-39800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-42800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-51200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-47100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-48500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-38900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-39100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-28600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-27300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-17900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-13600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-11600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-7800</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1511,8 +1544,9 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1520,37 +1554,37 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F20" s="3">
         <v>1700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1600</v>
-      </c>
-      <c r="G20" s="3">
-        <v>1500</v>
       </c>
       <c r="H20" s="3">
         <v>1500</v>
       </c>
       <c r="I20" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J20" s="3">
         <v>1200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>300</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>200</v>
-      </c>
-      <c r="O20" s="3">
-        <v>100</v>
       </c>
       <c r="P20" s="3">
         <v>100</v>
@@ -1565,28 +1599,31 @@
         <v>100</v>
       </c>
       <c r="T20" s="3">
+        <v>100</v>
+      </c>
+      <c r="U20" s="3">
         <v>300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-5700</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1594,73 +1631,76 @@
         <v>3</v>
       </c>
       <c r="E21" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="F21" s="3">
         <v>-16000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-26200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-22900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-33400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-26100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-25800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-38600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-41900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-50500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-46500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-48200</v>
-      </c>
-      <c r="P21" s="3">
-        <v>-38700</v>
       </c>
       <c r="Q21" s="3">
         <v>-38700</v>
       </c>
       <c r="R21" s="3">
+        <v>-38700</v>
+      </c>
+      <c r="S21" s="3">
         <v>-28300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-27000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-17500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-13100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-11300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-13400</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1733,82 +1773,88 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-16700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-16800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-27100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-23900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-34300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-27100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-26700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-39500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-42800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-51200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-46900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-48400</v>
-      </c>
-      <c r="P23" s="3">
-        <v>-38900</v>
       </c>
       <c r="Q23" s="3">
         <v>-38900</v>
       </c>
       <c r="R23" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="S23" s="3">
         <v>-28500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-27200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-17600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-13200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-11400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-13400</v>
       </c>
-      <c r="X23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1881,8 +1927,11 @@
       <c r="Z24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1955,156 +2004,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-16700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-16800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-27100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-23900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-34300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-27100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-26700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-39500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-42800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-51200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-46900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-48400</v>
-      </c>
-      <c r="P26" s="3">
-        <v>-38900</v>
       </c>
       <c r="Q26" s="3">
         <v>-38900</v>
       </c>
       <c r="R26" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="S26" s="3">
         <v>-28500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-27200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-17600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-13200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-11400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-13400</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-16700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-16800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-27100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-23900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-34300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-27100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-26700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-39500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-42800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-51200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-46900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-48400</v>
-      </c>
-      <c r="P27" s="3">
-        <v>-38900</v>
       </c>
       <c r="Q27" s="3">
         <v>-38900</v>
       </c>
       <c r="R27" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="S27" s="3">
         <v>-28500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-27200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-17600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-13200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-11400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-13400</v>
       </c>
-      <c r="X27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2177,8 +2235,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2251,8 +2312,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2325,8 +2389,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2399,8 +2466,11 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2408,37 +2478,37 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="F32" s="3">
         <v>-1700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1600</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-1500</v>
       </c>
       <c r="H32" s="3">
         <v>-1500</v>
       </c>
       <c r="I32" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="J32" s="3">
         <v>-1200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-300</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-200</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-100</v>
       </c>
       <c r="P32" s="3">
         <v>-100</v>
@@ -2453,102 +2523,108 @@
         <v>-100</v>
       </c>
       <c r="T32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U32" s="3">
         <v>-300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>5700</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-16700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-16800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-27100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-23900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-34300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-27100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-26700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-39500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-42800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-51200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-46900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-48400</v>
-      </c>
-      <c r="P33" s="3">
-        <v>-38900</v>
       </c>
       <c r="Q33" s="3">
         <v>-38900</v>
       </c>
       <c r="R33" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="S33" s="3">
         <v>-28500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-27200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-17600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-13200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-11400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-13400</v>
       </c>
-      <c r="X33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2621,161 +2697,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-16700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-16800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-27100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-23900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-34300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-27100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-26700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-39500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-42800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-51200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-46900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-48400</v>
-      </c>
-      <c r="P35" s="3">
-        <v>-38900</v>
       </c>
       <c r="Q35" s="3">
         <v>-38900</v>
       </c>
       <c r="R35" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="S35" s="3">
         <v>-28500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-27200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-17600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-13200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-11400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-13400</v>
       </c>
-      <c r="X35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2802,8 +2887,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2830,65 +2916,66 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>24800</v>
+      </c>
+      <c r="E41" s="3">
         <v>36800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>21700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>33600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>30300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>33400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>34600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>62600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>91100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>101600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>129000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>162900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>215500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>249500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>135000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>200600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>353400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>366800</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2904,59 +2991,62 @@
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>67000</v>
+      </c>
+      <c r="E42" s="3">
         <v>67800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>92600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>99200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>121200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>134400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>155000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>151200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>148100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>165500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>186800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>191500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>192300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>188100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>169800</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>135100</v>
       </c>
-      <c r="S42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2972,14 +3062,17 @@
       <c r="X42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y42" s="3">
-        <v>0</v>
+      <c r="Y42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3052,8 +3145,11 @@
       <c r="Z43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3126,65 +3222,68 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E45" s="3">
         <v>3800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>7400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>8800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>11300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>15900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>9300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>12100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>11000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>13400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>12400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>13800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>14800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>15300</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3200,65 +3299,68 @@
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>95000</v>
+      </c>
+      <c r="E46" s="3">
         <v>108300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>118000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>135700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>153600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>171600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>197000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>222500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>250600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>283000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>325100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>366500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>418800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>450900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>317200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>349500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>368200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>382100</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3274,8 +3376,11 @@
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3348,64 +3453,67 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>29900</v>
+      </c>
+      <c r="E48" s="3">
         <v>31600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>32200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>33100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>39600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>41200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>42200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>42800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>43600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>44500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>23800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>17800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>13500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>900</v>
-      </c>
-      <c r="S48" s="3">
-        <v>1100</v>
       </c>
       <c r="T48" s="3">
         <v>1100</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
+      <c r="U48" s="3">
+        <v>1100</v>
       </c>
       <c r="V48" s="3" t="s">
         <v>3</v>
@@ -3422,8 +3530,11 @@
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3496,8 +3607,11 @@
       <c r="Z49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3570,8 +3684,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3644,16 +3761,19 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>500</v>
+      </c>
+      <c r="E52" s="3">
         <v>700</v>
-      </c>
-      <c r="E52" s="3">
-        <v>400</v>
       </c>
       <c r="F52" s="3">
         <v>400</v>
@@ -3665,44 +3785,44 @@
         <v>400</v>
       </c>
       <c r="I52" s="3">
+        <v>400</v>
+      </c>
+      <c r="J52" s="3">
         <v>4300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>5700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>6200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>7200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>7600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>8000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>8300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>8800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>9200</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3718,8 +3838,11 @@
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3792,65 +3915,68 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>125400</v>
+      </c>
+      <c r="E54" s="3">
         <v>140500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>150500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>169300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>193700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>213200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>243500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>270100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>299400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>333200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>355100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>390900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>439500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>465200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>328000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>358700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>378100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>392400</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3866,8 +3992,11 @@
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3894,8 +4023,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3922,65 +4052,66 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>600</v>
+      </c>
+      <c r="E57" s="3">
         <v>1700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>8200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>9100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>9400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>9000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>16400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>6200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>7200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2500</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3996,8 +4127,11 @@
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4070,65 +4204,68 @@
       <c r="Z58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E59" s="3">
         <v>11200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>15000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>17100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>16500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>14200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>14300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>17100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>18900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>18300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>20100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>13300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>14800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>13200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>15900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>15700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>6900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2700</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4144,65 +4281,68 @@
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E60" s="3">
         <v>12800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>16300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>19800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>19900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>17200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>18400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>21600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>27100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>27500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>29500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>22300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>31200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>19500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>21200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>19100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>14100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>5200</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4218,8 +4358,11 @@
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4292,65 +4435,68 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>22500</v>
+      </c>
+      <c r="E62" s="3">
         <v>22800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>22900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>23200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>23400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>25600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>23800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>24000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>24200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>24400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>6900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>6500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>6000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>500</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4366,8 +4512,11 @@
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4440,8 +4589,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4514,8 +4666,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4588,65 +4743,68 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>34800</v>
+      </c>
+      <c r="E66" s="3">
         <v>35600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>39300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>43000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>43300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>42900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>42200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>45700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>51400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>51900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>36400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>28700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>37300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>23700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>23300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>19800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>14700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5800</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4662,8 +4820,11 @@
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4690,8 +4851,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4764,8 +4926,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4838,8 +5003,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4912,8 +5080,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4986,65 +5157,68 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-627200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-611200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-594500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-577700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-550600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-526700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-492400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-465300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-438600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-399100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-356300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-305100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-258200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-209800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-170900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-132000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-103400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-76200</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5060,8 +5234,11 @@
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5134,8 +5311,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5208,8 +5388,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5282,65 +5465,68 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>90600</v>
+      </c>
+      <c r="E76" s="3">
         <v>104900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>111300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>126300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>150400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>170400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>201400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>224400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>248000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>281300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>318700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>362200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>402300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>441500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>304700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>338900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>363400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>386700</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5356,8 +5542,11 @@
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5430,161 +5619,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-16700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-16800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-27100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-23900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-34300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-27100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-26700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-39500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-42800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-51200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-46900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-48400</v>
-      </c>
-      <c r="P81" s="3">
-        <v>-38900</v>
       </c>
       <c r="Q81" s="3">
         <v>-38900</v>
       </c>
       <c r="R81" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="S81" s="3">
         <v>-28500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-27200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-17600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-13200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-11400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-13400</v>
       </c>
-      <c r="X81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5611,8 +5809,9 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5623,7 +5822,7 @@
         <v>800</v>
       </c>
       <c r="F83" s="3">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="G83" s="3">
         <v>1000</v>
@@ -5632,7 +5831,7 @@
         <v>1000</v>
       </c>
       <c r="I83" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="J83" s="3">
         <v>900</v>
@@ -5644,29 +5843,29 @@
         <v>900</v>
       </c>
       <c r="M83" s="3">
+        <v>900</v>
+      </c>
+      <c r="N83" s="3">
         <v>700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>500</v>
-      </c>
-      <c r="O83" s="3">
-        <v>200</v>
       </c>
       <c r="P83" s="3">
         <v>200</v>
       </c>
       <c r="Q83" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="R83" s="3">
         <v>300</v>
       </c>
       <c r="S83" s="3">
+        <v>300</v>
+      </c>
+      <c r="T83" s="3">
         <v>200</v>
       </c>
-      <c r="T83" s="3">
-        <v>0</v>
-      </c>
       <c r="U83" s="3">
         <v>0</v>
       </c>
@@ -5676,8 +5875,8 @@
       <c r="W83" s="3">
         <v>0</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>3</v>
+      <c r="X83" s="3">
+        <v>0</v>
       </c>
       <c r="Y83" s="3" t="s">
         <v>3</v>
@@ -5685,8 +5884,11 @@
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5759,8 +5961,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5833,8 +6038,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5907,8 +6115,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5981,8 +6192,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6055,82 +6269,88 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-18900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-19500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-19200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-17100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-22400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-24000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-23400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-26100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-44700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-30800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-41100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-24300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-30700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-29400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-17500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-11700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-21900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-17500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-11400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-10800</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6157,8 +6377,9 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6187,25 +6408,25 @@
         <v>-800</v>
       </c>
       <c r="L91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="M91" s="3">
         <v>-2200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-7300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-11500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4000</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-800</v>
       </c>
       <c r="Q91" s="3">
         <v>-800</v>
       </c>
       <c r="R91" s="3">
-        <v>-100</v>
+        <v>-800</v>
       </c>
       <c r="S91" s="3">
         <v>-100</v>
@@ -6214,25 +6435,28 @@
         <v>-100</v>
       </c>
       <c r="U91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
         <v>-100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-200</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6305,8 +6529,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6379,82 +6606,88 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E94" s="3">
         <v>25300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>7600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>22500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>14000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>21200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-4800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>16000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>17300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-11600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-10300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-20400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-36500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-135400</v>
-      </c>
-      <c r="S94" s="3">
-        <v>-100</v>
       </c>
       <c r="T94" s="3">
         <v>-100</v>
       </c>
       <c r="U94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
         <v>-100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-700</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6481,8 +6714,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6555,8 +6789,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6629,8 +6866,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6703,8 +6943,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6777,82 +7020,88 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>100</v>
+      </c>
+      <c r="E100" s="3">
         <v>8700</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
         <v>0</v>
       </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>100</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>-600</v>
-      </c>
-      <c r="J100" s="3">
-        <v>-400</v>
       </c>
       <c r="K100" s="3">
         <v>-400</v>
       </c>
       <c r="L100" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>500</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>165600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>400</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>-1600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>229900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>109900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>46300</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6925,78 +7174,84 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="E102" s="3">
         <v>15100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-11900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>3300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-3100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-28000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-28600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-10500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-27400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-33900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-52600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-34100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>114500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-65600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-152900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-13400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>208000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-18300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>98400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>34900</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PASG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PASG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="92">
   <si>
     <t>PASG</t>
   </si>
@@ -656,143 +656,147 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
+      <c r="E8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -845,8 +849,11 @@
       <c r="AA8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -922,8 +929,11 @@
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -999,8 +1009,11 @@
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1028,85 +1041,89 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E12" s="3">
         <v>10400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>11500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>12200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>15100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>17300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>16800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>17700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>16900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>26800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>27700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>34000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>32100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>33100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>26500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>28900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>20800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>19900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>13100</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>10000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>10400</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>6800</v>
       </c>
-      <c r="Y12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1182,31 +1199,34 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E14" s="3">
         <v>400</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="H14" s="3">
         <v>5400</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
+      <c r="J14" s="3">
+        <v>11300</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
@@ -1217,8 +1237,8 @@
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
@@ -1259,31 +1279,34 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1336,8 +1359,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1362,162 +1388,169 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>17400</v>
+        <v>15900</v>
       </c>
       <c r="E17" s="3">
+        <v>16900</v>
+      </c>
+      <c r="F17" s="3">
         <v>18100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>18400</v>
       </c>
-      <c r="G17" s="3">
-        <v>28700</v>
-      </c>
       <c r="H17" s="3">
+        <v>23300</v>
+      </c>
+      <c r="I17" s="3">
         <v>25400</v>
       </c>
-      <c r="I17" s="3">
-        <v>35900</v>
-      </c>
       <c r="J17" s="3">
+        <v>24600</v>
+      </c>
+      <c r="K17" s="3">
         <v>28200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>27500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>39800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>42800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>51200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>47100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>48500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>38900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>39100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>28600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>27300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>17900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>13600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>11600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>7800</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>-15900</v>
       </c>
       <c r="E18" s="3">
+        <v>-16900</v>
+      </c>
+      <c r="F18" s="3">
         <v>-18100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-18400</v>
       </c>
-      <c r="G18" s="3">
-        <v>-28700</v>
-      </c>
       <c r="H18" s="3">
+        <v>-23300</v>
+      </c>
+      <c r="I18" s="3">
         <v>-25400</v>
       </c>
-      <c r="I18" s="3">
-        <v>-35900</v>
-      </c>
       <c r="J18" s="3">
+        <v>-24600</v>
+      </c>
+      <c r="K18" s="3">
         <v>-28200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-27500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-39800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-42800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-51200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-47100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-48500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-38900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-39100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-28600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-27300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-17900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-13600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-11600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-7800</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1545,49 +1578,50 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>-300</v>
       </c>
       <c r="E20" s="3">
-        <v>1300</v>
+        <v>-200</v>
       </c>
       <c r="F20" s="3">
-        <v>1700</v>
+        <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>1600</v>
+        <v>-200</v>
       </c>
       <c r="H20" s="3">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="I20" s="3">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K20" s="3">
         <v>1200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>300</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>200</v>
-      </c>
-      <c r="P20" s="3">
-        <v>100</v>
       </c>
       <c r="Q20" s="3">
         <v>100</v>
@@ -1602,128 +1636,134 @@
         <v>100</v>
       </c>
       <c r="U20" s="3">
+        <v>100</v>
+      </c>
+      <c r="V20" s="3">
         <v>300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-5700</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>-14900</v>
       </c>
       <c r="E21" s="3">
-        <v>-15900</v>
+        <v>-16000</v>
       </c>
       <c r="F21" s="3">
-        <v>-16000</v>
+        <v>-17200</v>
       </c>
       <c r="G21" s="3">
-        <v>-26200</v>
+        <v>-17500</v>
       </c>
       <c r="H21" s="3">
-        <v>-22900</v>
+        <v>-22400</v>
       </c>
       <c r="I21" s="3">
-        <v>-33400</v>
+        <v>-24400</v>
       </c>
       <c r="J21" s="3">
+        <v>-23200</v>
+      </c>
+      <c r="K21" s="3">
         <v>-26100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-25800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-38600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-41900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-50500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-46500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-48200</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>-38700</v>
       </c>
       <c r="R21" s="3">
         <v>-38700</v>
       </c>
       <c r="S21" s="3">
+        <v>-38700</v>
+      </c>
+      <c r="T21" s="3">
         <v>-28300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-27000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-17500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-13100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-11300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-13400</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1776,108 +1816,114 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-19300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-16000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-16700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-16800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-27100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-23900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-34300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-27100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-26700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-39500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-42800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-51200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-46900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-48400</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>-38900</v>
       </c>
       <c r="R23" s="3">
         <v>-38900</v>
       </c>
       <c r="S23" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="T23" s="3">
         <v>-28500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-27200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-17600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-13200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-11400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-13400</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1930,8 +1976,11 @@
       <c r="AA24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2007,162 +2056,171 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-19300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-16000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-16700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-16800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-27100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-23900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-34300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-27100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-26700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-39500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-42800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-51200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-46900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-48400</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>-38900</v>
       </c>
       <c r="R26" s="3">
         <v>-38900</v>
       </c>
       <c r="S26" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="T26" s="3">
         <v>-28500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-27200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-17600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-13200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-11400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-13400</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-19300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-16000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-16700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-16800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-27100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-23900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-34300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-27100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-26700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-39500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-42800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-51200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-46900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-48400</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>-38900</v>
       </c>
       <c r="R27" s="3">
         <v>-38900</v>
       </c>
       <c r="S27" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="T27" s="3">
         <v>-28500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-27200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-17600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-13200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-11400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-13400</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2238,8 +2296,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2315,8 +2376,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2392,8 +2456,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2469,49 +2536,52 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>300</v>
       </c>
       <c r="E32" s="3">
-        <v>-1300</v>
+        <v>200</v>
       </c>
       <c r="F32" s="3">
-        <v>-1700</v>
+        <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>-1600</v>
+        <v>200</v>
       </c>
       <c r="H32" s="3">
-        <v>-1500</v>
+        <v>0</v>
       </c>
       <c r="I32" s="3">
-        <v>-1500</v>
+        <v>0</v>
       </c>
       <c r="J32" s="3">
+        <v>400</v>
+      </c>
+      <c r="K32" s="3">
         <v>-1200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-300</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-200</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-100</v>
       </c>
       <c r="Q32" s="3">
         <v>-100</v>
@@ -2526,105 +2596,111 @@
         <v>-100</v>
       </c>
       <c r="U32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V32" s="3">
         <v>-300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>5700</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-19300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-16000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-16700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-16800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-27100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-23900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-34300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-27100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-26700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-39500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-42800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-51200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-46900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-48400</v>
-      </c>
-      <c r="Q33" s="3">
-        <v>-38900</v>
       </c>
       <c r="R33" s="3">
         <v>-38900</v>
       </c>
       <c r="S33" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="T33" s="3">
         <v>-28500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-27200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-17600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-13200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-11400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-13400</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2700,167 +2776,176 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-19300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-16000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-16700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-16800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-27100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-23900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-34300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-27100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-26700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-39500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-42800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-51200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-46900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-48400</v>
-      </c>
-      <c r="Q35" s="3">
-        <v>-38900</v>
       </c>
       <c r="R35" s="3">
         <v>-38900</v>
       </c>
       <c r="S35" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="T35" s="3">
         <v>-28500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-27200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-17600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-13200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-11400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-13400</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2888,8 +2973,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2917,68 +3003,69 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>32300</v>
+      </c>
+      <c r="E41" s="3">
         <v>24800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>36800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>21700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>33600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>30300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>33400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>34600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>62600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>91100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>101600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>129000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>162900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>215500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>249500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>135000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>200600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>353400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>366800</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2994,62 +3081,65 @@
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>52500</v>
+      </c>
+      <c r="E42" s="3">
         <v>67000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>67800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>92600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>99200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>121200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>134400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>155000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>151200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>148100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>165500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>186800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>191500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>192300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>188100</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>169800</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>135100</v>
       </c>
-      <c r="T42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3065,37 +3155,40 @@
       <c r="Y42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z42" s="3">
-        <v>0</v>
+      <c r="Z42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -3148,31 +3241,34 @@
       <c r="AA43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3225,68 +3321,71 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>3200</v>
+        <v>1200</v>
       </c>
       <c r="E45" s="3">
-        <v>3800</v>
+        <v>1800</v>
       </c>
       <c r="F45" s="3">
-        <v>3700</v>
+        <v>2000</v>
       </c>
       <c r="G45" s="3">
-        <v>2900</v>
+        <v>2700</v>
       </c>
       <c r="H45" s="3">
-        <v>2100</v>
+        <v>1600</v>
       </c>
       <c r="I45" s="3">
-        <v>3800</v>
+        <v>900</v>
       </c>
       <c r="J45" s="3">
+        <v>2200</v>
+      </c>
+      <c r="K45" s="3">
         <v>7400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>8800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>11300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>15900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>9300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>12100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>11000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>13400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>12400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>13800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>14800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>15300</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3302,68 +3401,71 @@
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>87200</v>
+      </c>
+      <c r="E46" s="3">
         <v>95000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>108300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>118000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>135700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>153600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>171600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>197000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>222500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>250600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>283000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>325100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>366500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>418800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>450900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>317200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>349500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>368200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>382100</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3379,31 +3481,34 @@
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -3456,67 +3561,70 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>24100</v>
+      </c>
+      <c r="E48" s="3">
         <v>29900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>31600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>32200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>33100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>39600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>41200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>42200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>42800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>43600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>44500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>23800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>17800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>13500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>900</v>
-      </c>
-      <c r="T48" s="3">
-        <v>1100</v>
       </c>
       <c r="U48" s="3">
         <v>1100</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>3</v>
+      <c r="V48" s="3">
+        <v>1100</v>
       </c>
       <c r="W48" s="3" t="s">
         <v>3</v>
@@ -3533,8 +3641,11 @@
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3610,8 +3721,11 @@
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3687,8 +3801,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3764,8 +3881,11 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3773,10 +3893,10 @@
         <v>500</v>
       </c>
       <c r="E52" s="3">
+        <v>500</v>
+      </c>
+      <c r="F52" s="3">
         <v>700</v>
-      </c>
-      <c r="F52" s="3">
-        <v>400</v>
       </c>
       <c r="G52" s="3">
         <v>400</v>
@@ -3788,44 +3908,44 @@
         <v>400</v>
       </c>
       <c r="J52" s="3">
+        <v>400</v>
+      </c>
+      <c r="K52" s="3">
         <v>4300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>5200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>7200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>7600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>8000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>8300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>8800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>9200</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3841,8 +3961,11 @@
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3918,68 +4041,71 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>111800</v>
+      </c>
+      <c r="E54" s="3">
         <v>125400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>140500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>150500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>169300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>193700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>213200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>243500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>270100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>299400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>333200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>355100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>390900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>439500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>465200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>328000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>358700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>378100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>392400</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3995,8 +4121,11 @@
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4024,8 +4153,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4053,68 +4183,69 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E57" s="3">
         <v>600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>8200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>9100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>9400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>9000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>16400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>6200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>5300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>7200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2500</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4130,31 +4261,34 @@
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>3700</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>3700</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>3700</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>3400</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>3300</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>3300</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>3300</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -4207,68 +4341,71 @@
       <c r="AA58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>11800</v>
+        <v>6000</v>
       </c>
       <c r="E59" s="3">
-        <v>11200</v>
-      </c>
-      <c r="F59" s="3">
-        <v>15000</v>
+        <v>2500</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G59" s="3">
+        <v>2000</v>
+      </c>
+      <c r="H59" s="3">
+        <v>4000</v>
+      </c>
+      <c r="I59" s="3">
+        <v>5000</v>
+      </c>
+      <c r="J59" s="3">
+        <v>4000</v>
+      </c>
+      <c r="K59" s="3">
+        <v>14300</v>
+      </c>
+      <c r="L59" s="3">
         <v>17100</v>
       </c>
-      <c r="H59" s="3">
-        <v>16500</v>
-      </c>
-      <c r="I59" s="3">
-        <v>14200</v>
-      </c>
-      <c r="J59" s="3">
-        <v>14300</v>
-      </c>
-      <c r="K59" s="3">
-        <v>17100</v>
-      </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>18900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>18300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>20100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>13300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>14800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>13200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>15900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>15700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>6900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2700</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4284,68 +4421,71 @@
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E60" s="3">
         <v>12400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>12800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>16300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>19800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>19900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>17200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>18400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>21600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>27100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>27500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>29500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>22300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>31200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>19500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>21200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>19100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>14100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>5200</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4361,31 +4501,34 @@
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>22100</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>22500</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>22800</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>22900</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>23200</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>23400</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>23600</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -4438,68 +4581,71 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>22500</v>
-      </c>
-      <c r="E62" s="3">
-        <v>22800</v>
-      </c>
-      <c r="F62" s="3">
-        <v>22900</v>
-      </c>
-      <c r="G62" s="3">
-        <v>23200</v>
-      </c>
-      <c r="H62" s="3">
-        <v>23400</v>
-      </c>
-      <c r="I62" s="3">
-        <v>25600</v>
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J62" s="3">
+        <v>2000</v>
+      </c>
+      <c r="K62" s="3">
         <v>23800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>24000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>24200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>24400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>6900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>6500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>6000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>4200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>500</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4515,8 +4661,11 @@
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4592,8 +4741,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4669,8 +4821,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4746,68 +4901,71 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>39000</v>
+      </c>
+      <c r="E66" s="3">
         <v>34800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>35600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>39300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>43000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>43300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>42900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>42200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>45700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>51400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>51900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>36400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>28700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>37300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>23700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>23300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>19800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>14700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>5800</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4823,8 +4981,11 @@
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4852,8 +5013,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4929,8 +5091,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5006,8 +5171,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5083,8 +5251,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5160,68 +5331,71 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-646500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-627200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-611200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-594500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-577700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-550600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-526700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-492400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-465300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-438600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-399100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-356300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-305100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-258200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-209800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-170900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-132000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-103400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-76200</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5237,8 +5411,11 @@
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5314,8 +5491,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5391,8 +5571,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5468,68 +5651,71 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>72700</v>
+      </c>
+      <c r="E76" s="3">
         <v>90600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>104900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>111300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>126300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>150400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>170400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>201400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>224400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>248000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>281300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>318700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>362200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>402300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>441500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>304700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>338900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>363400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>386700</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5545,8 +5731,11 @@
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5622,167 +5811,176 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-19300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-16000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-16700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-16800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-27100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-23900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-34300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-27100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-26700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-39500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-42800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-51200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-46900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-48400</v>
-      </c>
-      <c r="Q81" s="3">
-        <v>-38900</v>
       </c>
       <c r="R81" s="3">
         <v>-38900</v>
       </c>
       <c r="S81" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="T81" s="3">
         <v>-28500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-27200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-17600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-13200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-11400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-13400</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5810,28 +6008,29 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="E83" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="F83" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="G83" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="H83" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="I83" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="J83" s="3">
         <v>900</v>
@@ -5846,29 +6045,29 @@
         <v>900</v>
       </c>
       <c r="N83" s="3">
+        <v>900</v>
+      </c>
+      <c r="O83" s="3">
         <v>700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>500</v>
-      </c>
-      <c r="P83" s="3">
-        <v>200</v>
       </c>
       <c r="Q83" s="3">
         <v>200</v>
       </c>
       <c r="R83" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="S83" s="3">
         <v>300</v>
       </c>
       <c r="T83" s="3">
+        <v>300</v>
+      </c>
+      <c r="U83" s="3">
         <v>200</v>
       </c>
-      <c r="U83" s="3">
-        <v>0</v>
-      </c>
       <c r="V83" s="3">
         <v>0</v>
       </c>
@@ -5878,8 +6077,8 @@
       <c r="X83" s="3">
         <v>0</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>3</v>
+      <c r="Y83" s="3">
+        <v>0</v>
       </c>
       <c r="Z83" s="3" t="s">
         <v>3</v>
@@ -5887,8 +6086,11 @@
       <c r="AA83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5964,8 +6166,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6041,8 +6246,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6118,8 +6326,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6195,8 +6406,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6272,85 +6486,91 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-13100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-18900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-19500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-19200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-17100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-22400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-24000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-23400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-26100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-44700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-30800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-41100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-24300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-30700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-29400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-17500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-11700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-21900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-17500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-11400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-10800</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6378,31 +6598,32 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
         <v>0</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
+      <c r="E91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-500</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-1700</v>
-      </c>
       <c r="J91" s="3">
-        <v>-800</v>
+        <v>0</v>
       </c>
       <c r="K91" s="3">
         <v>-800</v>
@@ -6411,25 +6632,25 @@
         <v>-800</v>
       </c>
       <c r="M91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="N91" s="3">
         <v>-2200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-7300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-11500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4000</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-800</v>
       </c>
       <c r="R91" s="3">
         <v>-800</v>
       </c>
       <c r="S91" s="3">
-        <v>-100</v>
+        <v>-800</v>
       </c>
       <c r="T91" s="3">
         <v>-100</v>
@@ -6438,25 +6659,28 @@
         <v>-100</v>
       </c>
       <c r="V91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
         <v>-100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-200</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6532,8 +6756,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6609,85 +6836,91 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E94" s="3">
         <v>1000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>25300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>7600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>22500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>14000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>21200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-4800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>16000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>17300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-11600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-10300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-20400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-36500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-135400</v>
-      </c>
-      <c r="T94" s="3">
-        <v>-100</v>
       </c>
       <c r="U94" s="3">
         <v>-100</v>
       </c>
       <c r="V94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3">
         <v>-100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-700</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6715,31 +6948,32 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -6792,8 +7026,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6869,8 +7106,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6946,8 +7186,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7023,108 +7266,114 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>8700</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
         <v>0</v>
       </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>100</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="J100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K100" s="3">
         <v>-600</v>
-      </c>
-      <c r="K100" s="3">
-        <v>-400</v>
       </c>
       <c r="L100" s="3">
         <v>-400</v>
       </c>
       <c r="M100" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>500</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>165600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>400</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>-1600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>229900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>109900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>46300</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -7177,81 +7426,87 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-12000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>15100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-11900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>3300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-3100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-28000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-28600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-10500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-27400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-33900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-52600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-34100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>114500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-65600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-152900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-13400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>208000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-18300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>98400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>34900</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PASG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PASG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="92">
   <si>
     <t>PASG</t>
   </si>
@@ -656,124 +656,127 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AB7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -798,8 +801,8 @@
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
+      <c r="K8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L8" s="3">
         <v>0</v>
@@ -852,8 +855,11 @@
       <c r="AB8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -932,8 +938,11 @@
       <c r="AB9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1012,8 +1021,11 @@
       <c r="AB10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1042,88 +1054,92 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E12" s="3">
         <v>8700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>10400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>11500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>12200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>15100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>17300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>16800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>17700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>16900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>26800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>27700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>34000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>32100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>33100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>26500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>28900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>20800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>19900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>13100</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>10000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>10400</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>6800</v>
       </c>
-      <c r="Z12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1202,35 +1218,38 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>4800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>400</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3">
-        <v>2000</v>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>5400</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
         <v>11300</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1240,8 +1259,8 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1282,13 +1301,16 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="E15" s="3">
         <v>800</v>
@@ -1300,7 +1322,7 @@
         <v>800</v>
       </c>
       <c r="H15" s="3">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="I15" s="3">
         <v>1000</v>
@@ -1309,7 +1331,7 @@
         <v>1000</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1362,8 +1384,11 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1389,168 +1414,175 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E17" s="3">
         <v>15900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>16900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>18100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>18400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>23300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>25400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>24600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>28200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>27500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>39800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>42800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>51200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>47100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>48500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>38900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>39100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>28600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>27300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>17900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>13600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>11600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>7800</v>
       </c>
-      <c r="Z17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-14300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-15900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-16900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-18100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-18400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-23300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-25400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-24600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-28200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-27500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-39800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-42800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-51200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-47100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-48500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-38900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-39100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-28600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-27300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-17900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-13600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-11600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-7800</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1579,52 +1611,53 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E20" s="3">
         <v>-300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-200</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>-200</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
         <v>0</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>-400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>300</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>200</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>100</v>
       </c>
       <c r="R20" s="3">
         <v>100</v>
@@ -1639,108 +1672,114 @@
         <v>100</v>
       </c>
       <c r="V20" s="3">
+        <v>100</v>
+      </c>
+      <c r="W20" s="3">
         <v>300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-5700</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-12800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-14900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-16000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-17200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-17500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-22400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-24400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-23200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-26100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-25800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-38600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-41900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-50500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-46500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-48200</v>
-      </c>
-      <c r="R21" s="3">
-        <v>-38700</v>
       </c>
       <c r="S21" s="3">
         <v>-38700</v>
       </c>
       <c r="T21" s="3">
+        <v>-38700</v>
+      </c>
+      <c r="U21" s="3">
         <v>-28300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-27000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-17500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-13100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-11300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-13400</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1765,8 +1804,8 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1819,88 +1858,94 @@
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-19300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-16000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-16700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-16800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-27100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-23900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-34300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-27100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-26700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-39500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-42800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-51200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-46900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-48400</v>
-      </c>
-      <c r="R23" s="3">
-        <v>-38900</v>
       </c>
       <c r="S23" s="3">
         <v>-38900</v>
       </c>
       <c r="T23" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="U23" s="3">
         <v>-28500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-27200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-17600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-13200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-11400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-13400</v>
       </c>
-      <c r="Z23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1925,8 +1970,8 @@
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -1979,8 +2024,11 @@
       <c r="AB24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2059,168 +2107,177 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-19300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-16000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-16700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-16800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-27100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-23900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-34300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-27100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-26700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-39500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-42800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-51200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-46900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-48400</v>
-      </c>
-      <c r="R26" s="3">
-        <v>-38900</v>
       </c>
       <c r="S26" s="3">
         <v>-38900</v>
       </c>
       <c r="T26" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="U26" s="3">
         <v>-28500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-27200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-17600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-13200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-11400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-13400</v>
       </c>
-      <c r="Z26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-19300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-16000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-16700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-16800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-27100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-23900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-34300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-27100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-26700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-39500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-42800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-51200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-46900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-48400</v>
-      </c>
-      <c r="R27" s="3">
-        <v>-38900</v>
       </c>
       <c r="S27" s="3">
         <v>-38900</v>
       </c>
       <c r="T27" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="U27" s="3">
         <v>-28500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-27200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-17600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-13200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-11400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-13400</v>
       </c>
-      <c r="Z27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2299,8 +2356,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2379,8 +2439,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2459,8 +2522,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2539,52 +2605,55 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>700</v>
+      </c>
+      <c r="E32" s="3">
         <v>300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>200</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>200</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
         <v>0</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-300</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-200</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-100</v>
       </c>
       <c r="R32" s="3">
         <v>-100</v>
@@ -2599,108 +2668,114 @@
         <v>-100</v>
       </c>
       <c r="V32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W32" s="3">
         <v>-300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>5700</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-19300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-16000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-16700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-16800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-27100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-23900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-34300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-27100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-26700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-39500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-42800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-51200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-46900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-48400</v>
-      </c>
-      <c r="R33" s="3">
-        <v>-38900</v>
       </c>
       <c r="S33" s="3">
         <v>-38900</v>
       </c>
       <c r="T33" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="U33" s="3">
         <v>-28500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-27200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-17600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-13200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-11400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-13400</v>
       </c>
-      <c r="Z33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2779,173 +2854,182 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-19300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-16000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-16700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-16800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-27100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-23900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-34300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-27100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-26700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-39500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-42800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-51200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-46900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-48400</v>
-      </c>
-      <c r="R35" s="3">
-        <v>-38900</v>
       </c>
       <c r="S35" s="3">
         <v>-38900</v>
       </c>
       <c r="T35" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="U35" s="3">
         <v>-28500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-27200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-17600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-13200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-11400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-13400</v>
       </c>
-      <c r="Z35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AB38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2974,8 +3058,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3004,71 +3089,72 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>37600</v>
+      </c>
+      <c r="E41" s="3">
         <v>32300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>24800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>36800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>21700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>33600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>30300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>33400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>34600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>62600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>91100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>101600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>129000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>162900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>215500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>249500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>135000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>200600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>353400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>366800</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3084,65 +3170,68 @@
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>39200</v>
+      </c>
+      <c r="E42" s="3">
         <v>52500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>67000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>67800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>92600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>99200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>121200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>134400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>155000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>151200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>148100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>165500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>186800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>191500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>192300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>188100</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>169800</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>135100</v>
       </c>
-      <c r="U42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3158,14 +3247,17 @@
       <c r="Z42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA42" s="3">
-        <v>0</v>
+      <c r="AA42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3187,12 +3279,12 @@
       <c r="I43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J43" s="3">
+      <c r="J43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K43" s="3">
         <v>100</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
       <c r="L43" s="3">
         <v>0</v>
       </c>
@@ -3244,8 +3336,11 @@
       <c r="AB43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3270,8 +3365,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -3324,8 +3419,11 @@
       <c r="AB44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3333,62 +3431,62 @@
         <v>1200</v>
       </c>
       <c r="E45" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F45" s="3">
         <v>1800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>7400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>8800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>11300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>15900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>9300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>12100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>11000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>13400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>12400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>13800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>14800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>15300</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3404,71 +3502,74 @@
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>78800</v>
+      </c>
+      <c r="E46" s="3">
         <v>87200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>95000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>108300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>118000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>135700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>153600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>171600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>197000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>222500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>250600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>283000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>325100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>366500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>418800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>450900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>317200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>349500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>368200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>382100</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3484,8 +3585,11 @@
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3510,8 +3614,8 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -3564,70 +3668,73 @@
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>23100</v>
+      </c>
+      <c r="E48" s="3">
         <v>24100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>29900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>31600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>32200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>33100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>39600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>41200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>42200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>42800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>43600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>44500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>23800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>17800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>13500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>6600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>900</v>
-      </c>
-      <c r="U48" s="3">
-        <v>1100</v>
       </c>
       <c r="V48" s="3">
         <v>1100</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>3</v>
+      <c r="W48" s="3">
+        <v>1100</v>
       </c>
       <c r="X48" s="3" t="s">
         <v>3</v>
@@ -3644,8 +3751,11 @@
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3724,8 +3834,11 @@
       <c r="AB49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3804,8 +3917,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3884,8 +4000,11 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3896,10 +4015,10 @@
         <v>500</v>
       </c>
       <c r="F52" s="3">
+        <v>500</v>
+      </c>
+      <c r="G52" s="3">
         <v>700</v>
-      </c>
-      <c r="G52" s="3">
-        <v>400</v>
       </c>
       <c r="H52" s="3">
         <v>400</v>
@@ -3911,44 +4030,44 @@
         <v>400</v>
       </c>
       <c r="K52" s="3">
+        <v>400</v>
+      </c>
+      <c r="L52" s="3">
         <v>4300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>6700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>7200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>7600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>8000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>8300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>8800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>9200</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3964,8 +4083,11 @@
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4044,71 +4166,74 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>102400</v>
+      </c>
+      <c r="E54" s="3">
         <v>111800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>125400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>140500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>150500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>169300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>193700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>213200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>243500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>270100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>299400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>333200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>355100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>390900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>439500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>465200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>328000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>358700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>378100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>392400</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4124,8 +4249,11 @@
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4154,8 +4282,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4184,71 +4313,72 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>700</v>
+      </c>
+      <c r="E57" s="3">
         <v>1500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>8200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>9100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>9400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>9000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>16400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>6200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>5300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>7200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2500</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4264,8 +4394,11 @@
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4279,10 +4412,10 @@
         <v>3700</v>
       </c>
       <c r="G58" s="3">
+        <v>3700</v>
+      </c>
+      <c r="H58" s="3">
         <v>3400</v>
-      </c>
-      <c r="H58" s="3">
-        <v>3300</v>
       </c>
       <c r="I58" s="3">
         <v>3300</v>
@@ -4291,7 +4424,7 @@
         <v>3300</v>
       </c>
       <c r="K58" s="3">
-        <v>0</v>
+        <v>3300</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -4344,71 +4477,74 @@
       <c r="AB58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E59" s="3">
         <v>6000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2500</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G59" s="3">
+      <c r="G59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H59" s="3">
         <v>2000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>5000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>14300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>17100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>18900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>18300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>20100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>13300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>14800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>13200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>15900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>15700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>6900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2700</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4424,71 +4560,74 @@
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>19400</v>
+      </c>
+      <c r="E60" s="3">
         <v>17000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>12400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>12800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>16300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>19800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>19900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>17200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>18400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>21600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>27100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>27500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>29500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>22300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>31200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>19500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>21200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>19100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>14100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>5200</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4504,35 +4643,38 @@
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E61" s="3">
         <v>22100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>22500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>22800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>22900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>23200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>23400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>23600</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -4584,8 +4726,11 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4607,48 +4752,48 @@
       <c r="I62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J62" s="3">
+      <c r="J62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K62" s="3">
         <v>2000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>23800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>24000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>24200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>24400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>6900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>6500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>6000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>4200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>500</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4664,8 +4809,11 @@
       <c r="AB62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4744,8 +4892,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4824,8 +4975,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4904,71 +5058,74 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>41200</v>
+      </c>
+      <c r="E66" s="3">
         <v>39000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>34800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>35600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>39300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>43000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>43300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>42900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>42200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>45700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>51400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>51900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>36400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>28700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>37300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>23700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>23300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>19800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>14700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5800</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4984,8 +5141,11 @@
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5014,8 +5174,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5094,8 +5255,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5174,8 +5338,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5254,8 +5421,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5334,71 +5504,74 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-659200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-646500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-627200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-611200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-594500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-577700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-550600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-526700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-492400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-465300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-438600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-399100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-356300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-305100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-258200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-209800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-170900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-132000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-103400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-76200</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5414,8 +5587,11 @@
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5494,8 +5670,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5574,8 +5753,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5654,71 +5836,74 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>61300</v>
+      </c>
+      <c r="E76" s="3">
         <v>72700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>90600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>104900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>111300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>126300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>150400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>170400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>201400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>224400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>248000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>281300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>318700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>362200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>402300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>441500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>304700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>338900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>363400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>386700</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5734,8 +5919,11 @@
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5814,173 +6002,182 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AB80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-19300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-16000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-16700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-16800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-27100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-23900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-34300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-27100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-26700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-39500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-42800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-51200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-46900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-48400</v>
-      </c>
-      <c r="R81" s="3">
-        <v>-38900</v>
       </c>
       <c r="S81" s="3">
         <v>-38900</v>
       </c>
       <c r="T81" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="U81" s="3">
         <v>-28500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-27200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-17600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-13200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-11400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-13400</v>
       </c>
-      <c r="Z81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6009,13 +6206,14 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="E83" s="3">
         <v>1000</v>
@@ -6024,7 +6222,7 @@
         <v>1000</v>
       </c>
       <c r="G83" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="H83" s="3">
         <v>900</v>
@@ -6048,29 +6246,29 @@
         <v>900</v>
       </c>
       <c r="O83" s="3">
+        <v>900</v>
+      </c>
+      <c r="P83" s="3">
         <v>700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>500</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>200</v>
       </c>
       <c r="R83" s="3">
         <v>200</v>
       </c>
       <c r="S83" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="T83" s="3">
         <v>300</v>
       </c>
       <c r="U83" s="3">
+        <v>300</v>
+      </c>
+      <c r="V83" s="3">
         <v>200</v>
       </c>
-      <c r="V83" s="3">
-        <v>0</v>
-      </c>
       <c r="W83" s="3">
         <v>0</v>
       </c>
@@ -6080,8 +6278,8 @@
       <c r="Y83" s="3">
         <v>0</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>3</v>
+      <c r="Z83" s="3">
+        <v>0</v>
       </c>
       <c r="AA83" s="3" t="s">
         <v>3</v>
@@ -6089,8 +6287,11 @@
       <c r="AB83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6169,8 +6370,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6249,8 +6453,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6329,8 +6536,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6409,8 +6619,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6489,88 +6702,94 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-7400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-13100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-18900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-19500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-19200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-17100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-22400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-24000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-23400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-26100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-44700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-30800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-41100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-24300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-30700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-29400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-17500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-11700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-21900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-17500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-11400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-10800</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6599,34 +6818,35 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
         <v>0</v>
       </c>
-      <c r="E91" s="3" t="s">
-        <v>3</v>
+      <c r="E91" s="3">
+        <v>0</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H91" s="3">
         <v>0</v>
       </c>
       <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
-        <v>-800</v>
+        <v>0</v>
       </c>
       <c r="L91" s="3">
         <v>-800</v>
@@ -6635,25 +6855,25 @@
         <v>-800</v>
       </c>
       <c r="N91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="O91" s="3">
         <v>-2200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-7300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-11500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4000</v>
-      </c>
-      <c r="R91" s="3">
-        <v>-800</v>
       </c>
       <c r="S91" s="3">
         <v>-800</v>
       </c>
       <c r="T91" s="3">
-        <v>-100</v>
+        <v>-800</v>
       </c>
       <c r="U91" s="3">
         <v>-100</v>
@@ -6662,25 +6882,28 @@
         <v>-100</v>
       </c>
       <c r="W91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-200</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6759,8 +6982,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6839,88 +7065,94 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>13700</v>
+      </c>
+      <c r="E94" s="3">
         <v>15000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>1000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>25300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>7600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>22500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>14000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>21200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-4800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>16000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>17300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-11600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-10300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-20400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-36500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-135400</v>
-      </c>
-      <c r="U94" s="3">
-        <v>-100</v>
       </c>
       <c r="V94" s="3">
         <v>-100</v>
       </c>
       <c r="W94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3">
         <v>-100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-700</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6949,8 +7181,9 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6975,8 +7208,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -7029,8 +7262,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7109,8 +7345,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7189,8 +7428,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7269,8 +7511,11 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -7278,79 +7523,82 @@
         <v>0</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>8700</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
         <v>0</v>
       </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>100</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K100" s="3">
+      <c r="K100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L100" s="3">
         <v>-600</v>
-      </c>
-      <c r="L100" s="3">
-        <v>-400</v>
       </c>
       <c r="M100" s="3">
         <v>-400</v>
       </c>
       <c r="N100" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>500</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>165600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>400</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>-1600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>229900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>109900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>46300</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7375,8 +7623,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -7429,84 +7677,90 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E102" s="3">
         <v>7500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-12000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>15100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-11900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>3300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-3100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-28000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-28600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-10500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-27400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-33900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-52600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-34100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>114500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-65600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-152900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-13400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>208000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-18300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>98400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>34900</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PASG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PASG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="92">
   <si>
     <t>PASG</t>
   </si>
@@ -656,127 +656,131 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AC7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -804,8 +808,8 @@
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L8" s="3">
-        <v>0</v>
+      <c r="L8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M8" s="3">
         <v>0</v>
@@ -858,8 +862,11 @@
       <c r="AC8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -941,8 +948,11 @@
       <c r="AC9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1024,8 +1034,11 @@
       <c r="AC10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1055,91 +1068,95 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E12" s="3">
         <v>9600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>8700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>10400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>11500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>12200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>15100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>17300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>16800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>17700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>16900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>26800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>27700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>34000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>32100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>33100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>26500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>28900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>20800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>19900</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>13100</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>10000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>10400</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>6800</v>
       </c>
-      <c r="AA12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1221,38 +1238,41 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>2600</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>4800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>400</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>5400</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
         <v>11300</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1262,8 +1282,8 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1304,16 +1324,19 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>200</v>
+      </c>
+      <c r="E15" s="3">
         <v>700</v>
-      </c>
-      <c r="E15" s="3">
-        <v>800</v>
       </c>
       <c r="F15" s="3">
         <v>800</v>
@@ -1325,7 +1348,7 @@
         <v>800</v>
       </c>
       <c r="I15" s="3">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="J15" s="3">
         <v>1000</v>
@@ -1334,7 +1357,7 @@
         <v>1000</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1387,8 +1410,11 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1415,174 +1441,181 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E17" s="3">
         <v>14300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>15900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>16900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>18100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>18400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>23300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>25400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>24600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>28200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>27500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>39800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>42800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>51200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>47100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>48500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>38900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>39100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>28600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>27300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>17900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>13600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>11600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>7800</v>
       </c>
-      <c r="AA17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-13800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-14300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-15900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-16900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-18100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-18400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-23300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-25400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-24600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-28200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-27500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-39800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-42800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-51200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-47100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-48500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-38900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-39100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-28600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-27300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-17900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-13600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-11600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-7800</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1612,55 +1645,56 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-200</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>-200</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>-400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>300</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>200</v>
-      </c>
-      <c r="R20" s="3">
-        <v>100</v>
       </c>
       <c r="S20" s="3">
         <v>100</v>
@@ -1675,111 +1709,117 @@
         <v>100</v>
       </c>
       <c r="W20" s="3">
+        <v>100</v>
+      </c>
+      <c r="X20" s="3">
         <v>300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-5700</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-12800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-14900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-16000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-17200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-17500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-22400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-24400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-23200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-26100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-25800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-38600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-41900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-50500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-46500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-48200</v>
-      </c>
-      <c r="S21" s="3">
-        <v>-38700</v>
       </c>
       <c r="T21" s="3">
         <v>-38700</v>
       </c>
       <c r="U21" s="3">
+        <v>-38700</v>
+      </c>
+      <c r="V21" s="3">
         <v>-28300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-27000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-17500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-13100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-11300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-13400</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1807,8 +1847,8 @@
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1861,91 +1901,97 @@
       <c r="AC22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-12700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-19300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-16000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-16700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-16800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-27100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-23900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-34300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-27100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-26700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-39500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-42800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-51200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-46900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-48400</v>
-      </c>
-      <c r="S23" s="3">
-        <v>-38900</v>
       </c>
       <c r="T23" s="3">
         <v>-38900</v>
       </c>
       <c r="U23" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="V23" s="3">
         <v>-28500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-27200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-17600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-13200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-11400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-13400</v>
       </c>
-      <c r="AA23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1973,8 +2019,8 @@
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -2027,8 +2073,11 @@
       <c r="AC24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2110,174 +2159,183 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-12700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-19300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-16000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-16700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-16800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-27100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-23900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-34300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-27100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-26700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-39500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-42800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-51200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-46900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-48400</v>
-      </c>
-      <c r="S26" s="3">
-        <v>-38900</v>
       </c>
       <c r="T26" s="3">
         <v>-38900</v>
       </c>
       <c r="U26" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="V26" s="3">
         <v>-28500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-27200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-17600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-13200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-11400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-13400</v>
       </c>
-      <c r="AA26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-12700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-19300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-16000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-16700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-16800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-27100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-23900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-34300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-27100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-26700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-39500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-42800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-51200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-46900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-48400</v>
-      </c>
-      <c r="S27" s="3">
-        <v>-38900</v>
       </c>
       <c r="T27" s="3">
         <v>-38900</v>
       </c>
       <c r="U27" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="V27" s="3">
         <v>-28500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-27200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-17600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-13200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-11400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-13400</v>
       </c>
-      <c r="AA27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2359,8 +2417,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2442,8 +2503,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2525,8 +2589,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2608,55 +2675,58 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E32" s="3">
         <v>700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>200</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>200</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-300</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-200</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-100</v>
       </c>
       <c r="S32" s="3">
         <v>-100</v>
@@ -2671,111 +2741,117 @@
         <v>-100</v>
       </c>
       <c r="W32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="X32" s="3">
         <v>-300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>5700</v>
       </c>
-      <c r="AA32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-12700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-19300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-16000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-16700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-16800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-27100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-23900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-34300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-27100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-26700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-39500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-42800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-51200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-46900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-48400</v>
-      </c>
-      <c r="S33" s="3">
-        <v>-38900</v>
       </c>
       <c r="T33" s="3">
         <v>-38900</v>
       </c>
       <c r="U33" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="V33" s="3">
         <v>-28500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-27200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-17600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-13200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-11400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-13400</v>
       </c>
-      <c r="AA33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2857,179 +2933,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-12700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-19300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-16000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-16700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-16800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-27100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-23900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-34300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-27100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-26700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-39500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-42800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-51200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-46900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-48400</v>
-      </c>
-      <c r="S35" s="3">
-        <v>-38900</v>
       </c>
       <c r="T35" s="3">
         <v>-38900</v>
       </c>
       <c r="U35" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="V35" s="3">
         <v>-28500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-27200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-17600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-13200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-11400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-13400</v>
       </c>
-      <c r="AA35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AC38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3059,8 +3144,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3090,74 +3176,75 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>63400</v>
+      </c>
+      <c r="E41" s="3">
         <v>37600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>32300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>24800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>36800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>21700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>33600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>30300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>33400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>34600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>62600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>91100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>101600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>129000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>162900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>215500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>249500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>135000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>200600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>353400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>366800</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3173,68 +3260,71 @@
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>39200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>52500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>67000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>67800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>92600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>99200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>121200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>134400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>155000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>151200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>148100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>165500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>186800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>191500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>192300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>188100</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>169800</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>135100</v>
       </c>
-      <c r="V42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3250,14 +3340,17 @@
       <c r="AA42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB42" s="3">
-        <v>0</v>
+      <c r="AB42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3282,12 +3375,12 @@
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K43" s="3">
+      <c r="K43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L43" s="3">
         <v>100</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
       <c r="M43" s="3">
         <v>0</v>
       </c>
@@ -3339,8 +3432,11 @@
       <c r="AC43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3368,8 +3464,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -3422,8 +3518,11 @@
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3434,62 +3533,62 @@
         <v>1200</v>
       </c>
       <c r="F45" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G45" s="3">
         <v>1800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>7400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>8800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>11300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>15900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>9300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>12100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>11000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>13400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>12400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>13800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>14800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>15300</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3505,74 +3604,77 @@
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>66700</v>
+      </c>
+      <c r="E46" s="3">
         <v>78800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>87200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>95000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>108300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>118000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>135700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>153600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>171600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>197000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>222500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>250600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>283000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>325100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>366500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>418800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>450900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>317200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>349500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>368200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>382100</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3588,8 +3690,11 @@
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3617,8 +3722,8 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3671,73 +3776,76 @@
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>19100</v>
+      </c>
+      <c r="E48" s="3">
         <v>23100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>24100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>29900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>31600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>32200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>33100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>39600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>41200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>42200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>42800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>43600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>44500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>23800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>17800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>13500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>6600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>900</v>
-      </c>
-      <c r="V48" s="3">
-        <v>1100</v>
       </c>
       <c r="W48" s="3">
         <v>1100</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>3</v>
+      <c r="X48" s="3">
+        <v>1100</v>
       </c>
       <c r="Y48" s="3" t="s">
         <v>3</v>
@@ -3754,8 +3862,11 @@
       <c r="AC48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3837,8 +3948,11 @@
       <c r="AC49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3920,8 +4034,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4003,13 +4120,16 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="E52" s="3">
         <v>500</v>
@@ -4018,10 +4138,10 @@
         <v>500</v>
       </c>
       <c r="G52" s="3">
+        <v>500</v>
+      </c>
+      <c r="H52" s="3">
         <v>700</v>
-      </c>
-      <c r="H52" s="3">
-        <v>400</v>
       </c>
       <c r="I52" s="3">
         <v>400</v>
@@ -4033,44 +4153,44 @@
         <v>400</v>
       </c>
       <c r="L52" s="3">
+        <v>400</v>
+      </c>
+      <c r="M52" s="3">
         <v>4300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>5700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>6200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>6700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>7200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>7600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>8000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>8300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>8800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>9200</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4086,8 +4206,11 @@
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4169,74 +4292,77 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>86000</v>
+      </c>
+      <c r="E54" s="3">
         <v>102400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>111800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>125400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>140500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>150500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>169300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>193700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>213200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>243500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>270100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>299400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>333200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>355100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>390900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>439500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>465200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>328000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>358700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>378100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>392400</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4252,8 +4378,11 @@
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4283,8 +4412,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4314,74 +4444,75 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E57" s="3">
         <v>700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>8200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>9100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>9400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>9000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>16400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>6200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>5300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>7200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2500</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4397,13 +4528,16 @@
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>3700</v>
+        <v>3600</v>
       </c>
       <c r="E58" s="3">
         <v>3700</v>
@@ -4415,10 +4549,10 @@
         <v>3700</v>
       </c>
       <c r="H58" s="3">
+        <v>3700</v>
+      </c>
+      <c r="I58" s="3">
         <v>3400</v>
-      </c>
-      <c r="I58" s="3">
-        <v>3300</v>
       </c>
       <c r="J58" s="3">
         <v>3300</v>
@@ -4427,7 +4561,7 @@
         <v>3300</v>
       </c>
       <c r="L58" s="3">
-        <v>0</v>
+        <v>3300</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -4480,74 +4614,77 @@
       <c r="AC58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E59" s="3">
         <v>8200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>6000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2500</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I59" s="3">
         <v>2000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>14300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>17100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>18900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>18300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>20100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>13300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>14800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>13200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>15900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>15700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>6900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2700</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4563,74 +4700,77 @@
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>17800</v>
+      </c>
+      <c r="E60" s="3">
         <v>19400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>17000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>12400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>12800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>16300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>19800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>19900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>17200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>18400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>21600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>27100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>27500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>29500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>22300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>31200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>19500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>21200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>19100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>14100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>5200</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4646,38 +4786,41 @@
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>21500</v>
+      </c>
+      <c r="E61" s="3">
         <v>21800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>22100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>22500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>22800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>22900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>23200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>23400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>23600</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -4729,8 +4872,11 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4755,48 +4901,48 @@
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L62" s="3">
         <v>2000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>23800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>24000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>24200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>24400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>6900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>6500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>6000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>4200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>500</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4812,8 +4958,11 @@
       <c r="AC62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4895,8 +5044,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4978,8 +5130,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5061,74 +5216,77 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>39300</v>
+      </c>
+      <c r="E66" s="3">
         <v>41200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>39000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>34800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>35600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>39300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>43000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>43300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>42900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>42200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>45700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>51400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>51900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>36400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>28700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>37300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>23700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>23300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>19800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>14700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>5800</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5144,8 +5302,11 @@
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5175,8 +5336,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5258,8 +5420,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5341,8 +5506,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5424,8 +5592,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5507,74 +5678,77 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-674600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-659200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-646500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-627200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-611200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-594500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-577700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-550600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-526700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-492400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-465300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-438600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-399100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-356300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-305100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-258200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-209800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-170900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-132000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-103400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-76200</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5590,8 +5764,11 @@
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5673,8 +5850,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5756,8 +5936,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5839,74 +6022,77 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>46700</v>
+      </c>
+      <c r="E76" s="3">
         <v>61300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>72700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>90600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>104900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>111300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>126300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>150400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>170400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>201400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>224400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>248000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>281300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>318700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>362200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>402300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>441500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>304700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>338900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>363400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>386700</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5922,8 +6108,11 @@
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6005,179 +6194,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AC80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-12700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-19300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-16000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-16700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-16800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-27100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-23900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-34300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-27100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-26700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-39500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-42800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-51200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-46900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-48400</v>
-      </c>
-      <c r="S81" s="3">
-        <v>-38900</v>
       </c>
       <c r="T81" s="3">
         <v>-38900</v>
       </c>
       <c r="U81" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="V81" s="3">
         <v>-28500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-27200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-17600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-13200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-11400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-13400</v>
       </c>
-      <c r="AA81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6207,8 +6405,9 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6216,7 +6415,7 @@
         <v>800</v>
       </c>
       <c r="E83" s="3">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="F83" s="3">
         <v>1000</v>
@@ -6225,7 +6424,7 @@
         <v>1000</v>
       </c>
       <c r="H83" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="I83" s="3">
         <v>900</v>
@@ -6249,29 +6448,29 @@
         <v>900</v>
       </c>
       <c r="P83" s="3">
+        <v>900</v>
+      </c>
+      <c r="Q83" s="3">
         <v>700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>500</v>
-      </c>
-      <c r="R83" s="3">
-        <v>200</v>
       </c>
       <c r="S83" s="3">
         <v>200</v>
       </c>
       <c r="T83" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="U83" s="3">
         <v>300</v>
       </c>
       <c r="V83" s="3">
+        <v>300</v>
+      </c>
+      <c r="W83" s="3">
         <v>200</v>
       </c>
-      <c r="W83" s="3">
-        <v>0</v>
-      </c>
       <c r="X83" s="3">
         <v>0</v>
       </c>
@@ -6281,8 +6480,8 @@
       <c r="Z83" s="3">
         <v>0</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>3</v>
+      <c r="AA83" s="3">
+        <v>0</v>
       </c>
       <c r="AB83" s="3" t="s">
         <v>3</v>
@@ -6290,8 +6489,11 @@
       <c r="AC83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6373,8 +6575,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6456,8 +6661,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6539,8 +6747,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6622,8 +6833,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6705,91 +6919,97 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-13800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-8400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-7400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-13100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-18900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-19500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-19200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-17100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-22400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-24000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-23400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-26100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-44700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-30800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-41100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-24300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-30700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-29400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-17500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-11700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-21900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-17500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-11400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-10800</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6819,37 +7039,38 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>3</v>
+      <c r="F91" s="3">
+        <v>0</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I91" s="3">
         <v>0</v>
       </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
-        <v>-800</v>
+        <v>0</v>
       </c>
       <c r="M91" s="3">
         <v>-800</v>
@@ -6858,25 +7079,25 @@
         <v>-800</v>
       </c>
       <c r="O91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="P91" s="3">
         <v>-2200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-7300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-11500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4000</v>
-      </c>
-      <c r="S91" s="3">
-        <v>-800</v>
       </c>
       <c r="T91" s="3">
         <v>-800</v>
       </c>
       <c r="U91" s="3">
-        <v>-100</v>
+        <v>-800</v>
       </c>
       <c r="V91" s="3">
         <v>-100</v>
@@ -6885,25 +7106,28 @@
         <v>-100</v>
       </c>
       <c r="X91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-200</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6985,8 +7209,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7068,91 +7295,97 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>39600</v>
+      </c>
+      <c r="E94" s="3">
         <v>13700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>15000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>1000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>25300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>7600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>22500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>14000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>21200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>16000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>17300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-11600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-10300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-20400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-36500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-135400</v>
-      </c>
-      <c r="V94" s="3">
-        <v>-100</v>
       </c>
       <c r="W94" s="3">
         <v>-100</v>
       </c>
       <c r="X94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-700</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7182,8 +7415,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7211,8 +7445,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -7265,8 +7499,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7348,8 +7585,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7431,8 +7671,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7514,91 +7757,97 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
+      <c r="D100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E100" s="3">
         <v>0</v>
       </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>8700</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
         <v>0</v>
       </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>100</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L100" s="3">
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M100" s="3">
         <v>-600</v>
-      </c>
-      <c r="M100" s="3">
-        <v>-400</v>
       </c>
       <c r="N100" s="3">
         <v>-400</v>
       </c>
       <c r="O100" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>500</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>165600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>400</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>-1600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>229900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>109900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>46300</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7626,8 +7875,8 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -7680,87 +7929,93 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>25800</v>
+      </c>
+      <c r="E102" s="3">
         <v>5300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>7500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-12000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>15100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-11900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>3300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-3100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-28000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-28600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-10500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-27400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-33900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-52600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-34100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>114500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-65600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-152900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-13400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>208000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-18300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>98400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>34900</v>
       </c>
-      <c r="AA102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PASG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PASG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="92">
   <si>
     <t>PASG</t>
   </si>
@@ -656,131 +656,135 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AD7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -811,8 +815,8 @@
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
+      <c r="M8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N8" s="3">
         <v>0</v>
@@ -865,8 +869,11 @@
       <c r="AD8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -951,8 +958,11 @@
       <c r="AD9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1037,8 +1047,11 @@
       <c r="AD10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1069,94 +1082,98 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E12" s="3">
         <v>7700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>9600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>8700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>10400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>11500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>12200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>15100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>17300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>16800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>17700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>16900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>26800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>27700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>34000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>32100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>33100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>26500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>28900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>20800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>19900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>13100</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>10000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>10400</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>6800</v>
       </c>
-      <c r="AB12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1241,41 +1258,44 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
         <v>2600</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>4800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>400</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>5400</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
         <v>11300</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1285,8 +1305,8 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1327,8 +1347,11 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1336,10 +1359,10 @@
         <v>200</v>
       </c>
       <c r="E15" s="3">
+        <v>200</v>
+      </c>
+      <c r="F15" s="3">
         <v>700</v>
-      </c>
-      <c r="F15" s="3">
-        <v>800</v>
       </c>
       <c r="G15" s="3">
         <v>800</v>
@@ -1351,7 +1374,7 @@
         <v>800</v>
       </c>
       <c r="J15" s="3">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="K15" s="3">
         <v>1000</v>
@@ -1360,7 +1383,7 @@
         <v>1000</v>
       </c>
       <c r="M15" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1413,8 +1436,11 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1442,180 +1468,187 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E17" s="3">
         <v>13800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>14300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>15900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>16900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>18100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>18400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>23300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>25400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>24600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>28200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>27500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>39800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>42800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>51200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>47100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>48500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>38900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>39100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>28600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>27300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>17900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>13600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>11600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>7800</v>
       </c>
-      <c r="AB17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-10300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-13800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-14300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-15900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-16900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-18100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-18400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-23300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-25400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-24600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-28200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-27500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-39800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-42800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-51200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-47100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-48500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-38900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-39100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-28600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-27300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-17900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-13600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-11600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-7800</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1646,58 +1679,59 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-1100</v>
+        <v>500</v>
       </c>
       <c r="E20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F20" s="3">
         <v>-700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-200</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>-200</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>-400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>300</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>200</v>
-      </c>
-      <c r="S20" s="3">
-        <v>100</v>
       </c>
       <c r="T20" s="3">
         <v>100</v>
@@ -1712,114 +1746,120 @@
         <v>100</v>
       </c>
       <c r="X20" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y20" s="3">
         <v>300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-5700</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-12600</v>
+        <v>-10600</v>
       </c>
       <c r="E21" s="3">
+        <v>-13300</v>
+      </c>
+      <c r="F21" s="3">
         <v>-12800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-14900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-16000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-17200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-17500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-22400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-24400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-23200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-26100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-25800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-38600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-41900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-50500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-46500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-48200</v>
-      </c>
-      <c r="T21" s="3">
-        <v>-38700</v>
       </c>
       <c r="U21" s="3">
         <v>-38700</v>
       </c>
       <c r="V21" s="3">
+        <v>-38700</v>
+      </c>
+      <c r="W21" s="3">
         <v>-28300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-27000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-17500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-13100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-11300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-13400</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1850,8 +1890,8 @@
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1904,94 +1944,100 @@
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-15400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-12700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-19300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-16000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-16700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-16800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-27100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-23900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-34300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-27100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-26700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-39500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-42800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-51200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-46900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-48400</v>
-      </c>
-      <c r="T23" s="3">
-        <v>-38900</v>
       </c>
       <c r="U23" s="3">
         <v>-38900</v>
       </c>
       <c r="V23" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="W23" s="3">
         <v>-28500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-27200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-17600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-13200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-11400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-13400</v>
       </c>
-      <c r="AB23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2022,8 +2068,8 @@
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -2076,8 +2122,11 @@
       <c r="AD24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2162,180 +2211,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-15400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-12700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-19300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-16000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-16700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-16800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-27100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-23900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-34300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-27100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-26700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-39500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-42800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-51200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-46900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-48400</v>
-      </c>
-      <c r="T26" s="3">
-        <v>-38900</v>
       </c>
       <c r="U26" s="3">
         <v>-38900</v>
       </c>
       <c r="V26" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="W26" s="3">
         <v>-28500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-27200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-17600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-13200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-11400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-13400</v>
       </c>
-      <c r="AB26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-15400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-12700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-19300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-16000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-16700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-16800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-27100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-23900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-34300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-27100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-26700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-39500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-42800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-51200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-46900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-48400</v>
-      </c>
-      <c r="T27" s="3">
-        <v>-38900</v>
       </c>
       <c r="U27" s="3">
         <v>-38900</v>
       </c>
       <c r="V27" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="W27" s="3">
         <v>-28500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-27200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-17600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-13200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-11400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-13400</v>
       </c>
-      <c r="AB27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2420,8 +2478,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2506,8 +2567,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2592,8 +2656,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2678,58 +2745,61 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>1100</v>
+        <v>-500</v>
       </c>
       <c r="E32" s="3">
+        <v>400</v>
+      </c>
+      <c r="F32" s="3">
         <v>700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>200</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>200</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-300</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-200</v>
-      </c>
-      <c r="S32" s="3">
-        <v>-100</v>
       </c>
       <c r="T32" s="3">
         <v>-100</v>
@@ -2744,114 +2814,120 @@
         <v>-100</v>
       </c>
       <c r="X32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>5700</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-15400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-12700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-19300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-16000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-16700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-16800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-27100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-23900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-34300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-27100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-26700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-39500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-42800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-51200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-46900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-48400</v>
-      </c>
-      <c r="T33" s="3">
-        <v>-38900</v>
       </c>
       <c r="U33" s="3">
         <v>-38900</v>
       </c>
       <c r="V33" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="W33" s="3">
         <v>-28500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-27200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-17600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-13200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-11400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-13400</v>
       </c>
-      <c r="AB33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2936,185 +3012,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-15400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-12700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-19300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-16000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-16700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-16800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-27100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-23900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-34300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-27100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-26700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-39500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-42800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-51200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-46900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-48400</v>
-      </c>
-      <c r="T35" s="3">
-        <v>-38900</v>
       </c>
       <c r="U35" s="3">
         <v>-38900</v>
       </c>
       <c r="V35" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="W35" s="3">
         <v>-28500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-27200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-17600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-13200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-11400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-13400</v>
       </c>
-      <c r="AB35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AD38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3145,8 +3230,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3177,77 +3263,78 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>57600</v>
+      </c>
+      <c r="E41" s="3">
         <v>63400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>37600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>32300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>24800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>36800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>21700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>33600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>30300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>33400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>34600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>62600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>91100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>101600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>129000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>162900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>215500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>249500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>135000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>200600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>353400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>366800</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3263,8 +3350,11 @@
       <c r="AD41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3272,62 +3362,62 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>39200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>52500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>67000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>67800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>92600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>99200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>121200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>134400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>155000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>151200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>148100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>165500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>186800</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>191500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>192300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>188100</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>169800</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>135100</v>
       </c>
-      <c r="W42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3343,14 +3433,17 @@
       <c r="AB42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC42" s="3">
-        <v>0</v>
+      <c r="AC42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3378,12 +3471,12 @@
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L43" s="3">
+      <c r="L43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M43" s="3">
         <v>100</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
-      </c>
       <c r="N43" s="3">
         <v>0</v>
       </c>
@@ -3435,8 +3528,11 @@
       <c r="AD43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3467,8 +3563,8 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -3521,13 +3617,16 @@
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="E45" s="3">
         <v>1200</v>
@@ -3536,62 +3635,62 @@
         <v>1200</v>
       </c>
       <c r="G45" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H45" s="3">
         <v>1800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>7400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>8800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>11300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>15900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>9300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>12100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>11000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>13400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>12400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>13800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>14800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>15300</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3607,77 +3706,80 @@
       <c r="AD45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>60300</v>
+      </c>
+      <c r="E46" s="3">
         <v>66700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>78800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>87200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>95000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>108300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>118000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>135700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>153600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>171600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>197000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>222500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>250600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>283000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>325100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>366500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>418800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>450900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>317200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>349500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>368200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>382100</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3693,8 +3795,11 @@
       <c r="AD46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3725,8 +3830,8 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -3779,76 +3884,79 @@
       <c r="AD47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>18600</v>
+      </c>
+      <c r="E48" s="3">
         <v>19100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>23100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>24100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>29900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>31600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>32200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>33100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>39600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>41200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>42200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>42800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>43600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>44500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>23800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>17800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>13500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>6600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>900</v>
-      </c>
-      <c r="W48" s="3">
-        <v>1100</v>
       </c>
       <c r="X48" s="3">
         <v>1100</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>3</v>
+      <c r="Y48" s="3">
+        <v>1100</v>
       </c>
       <c r="Z48" s="3" t="s">
         <v>3</v>
@@ -3865,8 +3973,11 @@
       <c r="AD48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3951,8 +4062,11 @@
       <c r="AD49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4037,8 +4151,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4123,8 +4240,11 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4132,7 +4252,7 @@
         <v>300</v>
       </c>
       <c r="E52" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="F52" s="3">
         <v>500</v>
@@ -4141,10 +4261,10 @@
         <v>500</v>
       </c>
       <c r="H52" s="3">
+        <v>500</v>
+      </c>
+      <c r="I52" s="3">
         <v>700</v>
-      </c>
-      <c r="I52" s="3">
-        <v>400</v>
       </c>
       <c r="J52" s="3">
         <v>400</v>
@@ -4156,44 +4276,44 @@
         <v>400</v>
       </c>
       <c r="M52" s="3">
+        <v>400</v>
+      </c>
+      <c r="N52" s="3">
         <v>4300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>5200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>5700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>6200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>6700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>7200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>7600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>8000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>8300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>8800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>9200</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4209,8 +4329,11 @@
       <c r="AD52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4295,77 +4418,80 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>79200</v>
+      </c>
+      <c r="E54" s="3">
         <v>86000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>102400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>111800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>125400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>140500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>150500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>169300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>193700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>213200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>243500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>270100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>299400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>333200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>355100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>390900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>439500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>465200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>328000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>358700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>378100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>392400</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4381,8 +4507,11 @@
       <c r="AD54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4413,8 +4542,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4445,77 +4575,78 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E57" s="3">
         <v>1500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>8200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>9100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>9400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>9000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>16400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>6200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>5300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>7200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2500</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4531,8 +4662,11 @@
       <c r="AD57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4540,7 +4674,7 @@
         <v>3600</v>
       </c>
       <c r="E58" s="3">
-        <v>3700</v>
+        <v>3600</v>
       </c>
       <c r="F58" s="3">
         <v>3700</v>
@@ -4552,10 +4686,10 @@
         <v>3700</v>
       </c>
       <c r="I58" s="3">
+        <v>3700</v>
+      </c>
+      <c r="J58" s="3">
         <v>3400</v>
-      </c>
-      <c r="J58" s="3">
-        <v>3300</v>
       </c>
       <c r="K58" s="3">
         <v>3300</v>
@@ -4564,7 +4698,7 @@
         <v>3300</v>
       </c>
       <c r="M58" s="3">
-        <v>0</v>
+        <v>3300</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -4617,77 +4751,80 @@
       <c r="AD58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E59" s="3">
         <v>8700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>8200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>6000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2500</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I59" s="3">
+      <c r="I59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J59" s="3">
         <v>2000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>5000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>14300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>17100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>18900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>18300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>20100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>13300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>14800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>13200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>15900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>15700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>6900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2700</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4703,77 +4840,80 @@
       <c r="AD59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>19800</v>
+      </c>
+      <c r="E60" s="3">
         <v>17800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>19400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>17000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>12400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>12800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>16300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>19800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>19900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>17200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>18400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>21600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>27100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>27500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>29500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>22300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>31200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>19500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>21200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>19100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>14100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>5200</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4789,41 +4929,44 @@
       <c r="AD60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>21100</v>
+      </c>
+      <c r="E61" s="3">
         <v>21500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>21800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>22100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>22500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>22800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>22900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>23200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>23400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>23600</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -4875,8 +5018,11 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4904,48 +5050,48 @@
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3">
         <v>2000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>23800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>24000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>24200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>24400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>6900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>6500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>6000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>4200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>500</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4961,8 +5107,11 @@
       <c r="AD62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5047,8 +5196,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5133,8 +5285,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5219,77 +5374,80 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>40900</v>
+      </c>
+      <c r="E66" s="3">
         <v>39300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>41200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>39000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>34800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>35600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>39300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>43000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>43300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>42900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>42200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>45700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>51400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>51900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>36400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>28700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>37300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>23700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>23300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>19800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>14700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>5800</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5305,8 +5463,11 @@
       <c r="AD66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5337,8 +5498,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5423,8 +5585,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5509,8 +5674,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5595,8 +5763,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5681,77 +5852,80 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-684000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-674600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-659200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-646500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-627200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-611200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-594500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-577700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-550600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-526700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-492400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-465300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-438600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-399100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-356300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-305100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-258200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-209800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-170900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-132000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-103400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-76200</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5767,8 +5941,11 @@
       <c r="AD72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5853,8 +6030,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5939,8 +6119,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6025,77 +6208,80 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>38300</v>
+      </c>
+      <c r="E76" s="3">
         <v>46700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>61300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>72700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>90600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>104900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>111300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>126300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>150400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>170400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>201400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>224400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>248000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>281300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>318700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>362200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>402300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>441500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>304700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>338900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>363400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>386700</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6111,8 +6297,11 @@
       <c r="AD76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6197,185 +6386,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AD80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-15400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-12700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-19300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-16000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-16700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-16800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-27100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-23900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-34300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-27100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-26700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-39500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-42800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-51200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-46900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-48400</v>
-      </c>
-      <c r="T81" s="3">
-        <v>-38900</v>
       </c>
       <c r="U81" s="3">
         <v>-38900</v>
       </c>
       <c r="V81" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="W81" s="3">
         <v>-28500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-27200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-17600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-13200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-11400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-13400</v>
       </c>
-      <c r="AB81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6406,8 +6604,9 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6418,7 +6617,7 @@
         <v>800</v>
       </c>
       <c r="F83" s="3">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="G83" s="3">
         <v>1000</v>
@@ -6427,7 +6626,7 @@
         <v>1000</v>
       </c>
       <c r="I83" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="J83" s="3">
         <v>900</v>
@@ -6451,29 +6650,29 @@
         <v>900</v>
       </c>
       <c r="Q83" s="3">
+        <v>900</v>
+      </c>
+      <c r="R83" s="3">
         <v>700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>500</v>
-      </c>
-      <c r="S83" s="3">
-        <v>200</v>
       </c>
       <c r="T83" s="3">
         <v>200</v>
       </c>
       <c r="U83" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="V83" s="3">
         <v>300</v>
       </c>
       <c r="W83" s="3">
+        <v>300</v>
+      </c>
+      <c r="X83" s="3">
         <v>200</v>
       </c>
-      <c r="X83" s="3">
-        <v>0</v>
-      </c>
       <c r="Y83" s="3">
         <v>0</v>
       </c>
@@ -6483,8 +6682,8 @@
       <c r="AA83" s="3">
         <v>0</v>
       </c>
-      <c r="AB83" s="3" t="s">
-        <v>3</v>
+      <c r="AB83" s="3">
+        <v>0</v>
       </c>
       <c r="AC83" s="3" t="s">
         <v>3</v>
@@ -6492,8 +6691,11 @@
       <c r="AD83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6578,8 +6780,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6664,8 +6869,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6750,8 +6958,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6836,8 +7047,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6922,94 +7136,100 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-13800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-8400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-7400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-13100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-18900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-19500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-19200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-17100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-22400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-24000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-23400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-26100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-44700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-30800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-41100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-24300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-30700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-29400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-17500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-11700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-21900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-17500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-11400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-10800</v>
       </c>
-      <c r="AB89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7040,40 +7260,41 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
       </c>
-      <c r="G91" s="3" t="s">
-        <v>3</v>
+      <c r="G91" s="3">
+        <v>0</v>
       </c>
       <c r="H91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J91" s="3">
         <v>0</v>
       </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
-        <v>-800</v>
+        <v>0</v>
       </c>
       <c r="N91" s="3">
         <v>-800</v>
@@ -7082,25 +7303,25 @@
         <v>-800</v>
       </c>
       <c r="P91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-7300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-11500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4000</v>
-      </c>
-      <c r="T91" s="3">
-        <v>-800</v>
       </c>
       <c r="U91" s="3">
         <v>-800</v>
       </c>
       <c r="V91" s="3">
-        <v>-100</v>
+        <v>-800</v>
       </c>
       <c r="W91" s="3">
         <v>-100</v>
@@ -7109,25 +7330,28 @@
         <v>-100</v>
       </c>
       <c r="Y91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-200</v>
       </c>
-      <c r="AB91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7212,8 +7436,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7298,94 +7525,100 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>600</v>
+      </c>
+      <c r="E94" s="3">
         <v>39600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>13700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>15000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>1000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>25300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>7600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>22500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>14000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>21200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>16000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>17300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-11600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-10300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-20400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-36500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-135400</v>
-      </c>
-      <c r="W94" s="3">
-        <v>-100</v>
       </c>
       <c r="X94" s="3">
         <v>-100</v>
       </c>
       <c r="Y94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3">
         <v>-100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-700</v>
       </c>
-      <c r="AB94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7416,8 +7649,9 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7448,8 +7682,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -7502,8 +7736,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7588,8 +7825,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7674,8 +7914,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7760,94 +8003,100 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E100" s="3">
-        <v>0</v>
+      <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F100" s="3">
         <v>0</v>
       </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>8700</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
         <v>0</v>
       </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>100</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3">
         <v>-600</v>
-      </c>
-      <c r="N100" s="3">
-        <v>-400</v>
       </c>
       <c r="O100" s="3">
         <v>-400</v>
       </c>
       <c r="P100" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>500</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>165600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>400</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>-1600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>229900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>109900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>46300</v>
       </c>
-      <c r="AB100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7878,8 +8127,8 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -7932,90 +8181,96 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E102" s="3">
         <v>25800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>5300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>7500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-12000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>15100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-11900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>3300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-3100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-28000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-28600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-10500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-27400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-33900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-52600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-34100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>114500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-65600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-152900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-13400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>208000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-18300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>98400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>34900</v>
       </c>
-      <c r="AB102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PASG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PASG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="92">
   <si>
     <t>PASG</t>
   </si>
@@ -656,139 +656,142 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="32" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="33" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AE7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AF7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -825,8 +828,8 @@
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O8" s="3">
-        <v>0</v>
+      <c r="O8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P8" s="3">
         <v>0</v>
@@ -879,8 +882,11 @@
       <c r="AF8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -971,8 +977,11 @@
       <c r="AF9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1063,8 +1072,11 @@
       <c r="AF10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1097,100 +1109,104 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E12" s="3">
         <v>4300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>5800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>7700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>9600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>8700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>10400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>11500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>12200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>15100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>17300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>16800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>17700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>16900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>26800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>27700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>34000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>32100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>33100</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>26500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>28900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>20800</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>19900</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>13100</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>10000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>10400</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>6800</v>
       </c>
-      <c r="AD12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1281,47 +1297,50 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>3500</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3">
         <v>2600</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>4800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>400</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>5400</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3">
         <v>11300</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1331,8 +1350,8 @@
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
@@ -1373,8 +1392,11 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1388,10 +1410,10 @@
         <v>200</v>
       </c>
       <c r="G15" s="3">
+        <v>200</v>
+      </c>
+      <c r="H15" s="3">
         <v>700</v>
-      </c>
-      <c r="H15" s="3">
-        <v>800</v>
       </c>
       <c r="I15" s="3">
         <v>800</v>
@@ -1403,7 +1425,7 @@
         <v>800</v>
       </c>
       <c r="L15" s="3">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="M15" s="3">
         <v>1000</v>
@@ -1412,7 +1434,7 @@
         <v>1000</v>
       </c>
       <c r="O15" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="P15" s="3">
         <v>0</v>
@@ -1465,8 +1487,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1496,192 +1521,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E17" s="3">
         <v>8700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>10300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>13800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>14300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>15900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>16900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>18100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>18400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>23300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>25400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>24600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>28200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>27500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>39800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>42800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>51200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>47100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>48500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>38900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>39100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>28600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>27300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>17900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>13600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>11600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>7800</v>
       </c>
-      <c r="AD17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-10300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-8700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-10300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-13800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-14300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-15900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-16900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-18100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-18400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-23300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-25400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-24600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-28200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-27500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-39800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-42800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-51200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-47100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-48500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-38900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-39100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-28600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-27300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-17900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-13600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-11600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-7800</v>
       </c>
-      <c r="AD18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1714,8 +1746,9 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1723,55 +1756,55 @@
         <v>-400</v>
       </c>
       <c r="E20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F20" s="3">
         <v>500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-400</v>
       </c>
-      <c r="G20" s="3">
-        <v>-700</v>
-      </c>
       <c r="H20" s="3">
+        <v>2800</v>
+      </c>
+      <c r="I20" s="3">
         <v>-300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-200</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>-200</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>-400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>300</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>200</v>
-      </c>
-      <c r="U20" s="3">
-        <v>100</v>
       </c>
       <c r="V20" s="3">
         <v>100</v>
@@ -1786,120 +1819,126 @@
         <v>100</v>
       </c>
       <c r="Z20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA20" s="3">
         <v>300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-5700</v>
       </c>
-      <c r="AD20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-8100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-10600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-13300</v>
       </c>
-      <c r="G21" s="3">
-        <v>-12800</v>
-      </c>
       <c r="H21" s="3">
+        <v>-16300</v>
+      </c>
+      <c r="I21" s="3">
         <v>-14900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-16000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-17200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-17500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-22400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-24400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-23200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-26100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-25800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-38600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-41900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-50500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-46500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-48200</v>
-      </c>
-      <c r="V21" s="3">
-        <v>-38700</v>
       </c>
       <c r="W21" s="3">
         <v>-38700</v>
       </c>
       <c r="X21" s="3">
+        <v>-38700</v>
+      </c>
+      <c r="Y21" s="3">
         <v>-28300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-27000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-17500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-13100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-11300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-13400</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1936,8 +1975,8 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1990,100 +2029,106 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-7700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-9400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-15400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-12700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-19300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-16000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-16700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-16800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-27100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-23900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-34300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-27100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-26700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-39500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-42800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-51200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-46900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-48400</v>
-      </c>
-      <c r="V23" s="3">
-        <v>-38900</v>
       </c>
       <c r="W23" s="3">
         <v>-38900</v>
       </c>
       <c r="X23" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="Y23" s="3">
         <v>-28500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-27200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-17600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-13200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-11400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-13400</v>
       </c>
-      <c r="AD23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2120,8 +2165,8 @@
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P24" s="3">
         <v>0</v>
@@ -2174,8 +2219,11 @@
       <c r="AF24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2266,192 +2314,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-7700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-9400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-15400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-12700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-19300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-16000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-16700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-16800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-27100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-23900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-34300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-27100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-26700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-39500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-42800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-51200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-46900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-48400</v>
-      </c>
-      <c r="V26" s="3">
-        <v>-38900</v>
       </c>
       <c r="W26" s="3">
         <v>-38900</v>
       </c>
       <c r="X26" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="Y26" s="3">
         <v>-28500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-27200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-17600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-13200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-11400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-13400</v>
       </c>
-      <c r="AD26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-7700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-9400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-15400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-12700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-19300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-16000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-16700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-16800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-27100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-23900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-34300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-27100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-26700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-39500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-42800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-51200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-46900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-48400</v>
-      </c>
-      <c r="V27" s="3">
-        <v>-38900</v>
       </c>
       <c r="W27" s="3">
         <v>-38900</v>
       </c>
       <c r="X27" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="Y27" s="3">
         <v>-28500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-27200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-17600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-13200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-11400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-13400</v>
       </c>
-      <c r="AD27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2542,8 +2599,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2634,8 +2694,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2726,8 +2789,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2818,8 +2884,11 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2827,55 +2896,55 @@
         <v>400</v>
       </c>
       <c r="E32" s="3">
+        <v>400</v>
+      </c>
+      <c r="F32" s="3">
         <v>-500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>400</v>
       </c>
-      <c r="G32" s="3">
-        <v>700</v>
-      </c>
       <c r="H32" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="I32" s="3">
         <v>300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>200</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>200</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-300</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>-200</v>
-      </c>
-      <c r="U32" s="3">
-        <v>-100</v>
       </c>
       <c r="V32" s="3">
         <v>-100</v>
@@ -2890,120 +2959,126 @@
         <v>-100</v>
       </c>
       <c r="Z32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>5700</v>
       </c>
-      <c r="AD32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-7700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-9400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-15400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-12700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-19300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-16000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-16700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-16800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-27100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-23900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-34300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-27100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-26700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-39500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-42800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-51200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-46900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-48400</v>
-      </c>
-      <c r="V33" s="3">
-        <v>-38900</v>
       </c>
       <c r="W33" s="3">
         <v>-38900</v>
       </c>
       <c r="X33" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="Y33" s="3">
         <v>-28500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-27200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-17600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-13200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-11400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-13400</v>
       </c>
-      <c r="AD33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3094,197 +3169,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-7700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-9400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-15400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-12700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-19300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-16000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-16700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-16800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-27100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-23900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-34300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-27100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-26700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-39500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-42800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-51200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-46900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-48400</v>
-      </c>
-      <c r="V35" s="3">
-        <v>-38900</v>
       </c>
       <c r="W35" s="3">
         <v>-38900</v>
       </c>
       <c r="X35" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="Y35" s="3">
         <v>-28500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-27200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-17600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-13200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-11400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-13400</v>
       </c>
-      <c r="AD35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AE38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AF38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3317,8 +3401,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3351,83 +3436,84 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>46300</v>
+      </c>
+      <c r="E41" s="3">
         <v>52800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>57600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>63400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>37600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>32300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>24800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>36800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>21700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>33600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>30300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>33400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>34600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>62600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>91100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>101600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>129000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>162900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>215500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>249500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>135000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>200600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>353400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>366800</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3443,8 +3529,11 @@
       <c r="AF41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3458,62 +3547,62 @@
         <v>0</v>
       </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>39200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>52500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>67000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>67800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>92600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>99200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>121200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>134400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>155000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>151200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>148100</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>165500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>186800</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>191500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>192300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>188100</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>169800</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>135100</v>
       </c>
-      <c r="Y42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3529,14 +3618,17 @@
       <c r="AD42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE42" s="3">
-        <v>0</v>
+      <c r="AE42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3570,12 +3662,12 @@
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N43" s="3">
+      <c r="N43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O43" s="3">
         <v>100</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
-      </c>
       <c r="P43" s="3">
         <v>0</v>
       </c>
@@ -3627,8 +3719,11 @@
       <c r="AF43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3665,8 +3760,8 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -3719,19 +3814,22 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1300</v>
+        <v>800</v>
       </c>
       <c r="E45" s="3">
         <v>1300</v>
       </c>
       <c r="F45" s="3">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="G45" s="3">
         <v>1200</v>
@@ -3740,62 +3838,62 @@
         <v>1200</v>
       </c>
       <c r="I45" s="3">
+        <v>1200</v>
+      </c>
+      <c r="J45" s="3">
         <v>1800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>7400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>8800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>11300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>15900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>9300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>12100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>11000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>13400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>12400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>13800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>14800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>15300</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3811,83 +3909,86 @@
       <c r="AF45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>47800</v>
+      </c>
+      <c r="E46" s="3">
         <v>55700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>60300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>66700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>78800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>87200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>95000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>108300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>118000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>135700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>153600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>171600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>197000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>222500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>250600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>283000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>325100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>366500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>418800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>450900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>317200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>349500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>368200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>382100</v>
       </c>
-      <c r="AA46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3903,8 +4004,11 @@
       <c r="AF46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3941,8 +4045,8 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -3995,82 +4099,85 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E48" s="3">
         <v>18200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>18600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>19100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>23100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>24100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>29900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>31600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>32200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>33100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>39600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>41200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>42200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>42800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>43600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>44500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>23800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>17800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>13500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>6600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>900</v>
-      </c>
-      <c r="Y48" s="3">
-        <v>1100</v>
       </c>
       <c r="Z48" s="3">
         <v>1100</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>3</v>
+      <c r="AA48" s="3">
+        <v>1100</v>
       </c>
       <c r="AB48" s="3" t="s">
         <v>3</v>
@@ -4087,8 +4194,11 @@
       <c r="AF48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4179,8 +4289,11 @@
       <c r="AF49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4271,8 +4384,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4363,13 +4479,16 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E52" s="3">
         <v>300</v>
@@ -4378,7 +4497,7 @@
         <v>300</v>
       </c>
       <c r="G52" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="H52" s="3">
         <v>500</v>
@@ -4387,10 +4506,10 @@
         <v>500</v>
       </c>
       <c r="J52" s="3">
+        <v>500</v>
+      </c>
+      <c r="K52" s="3">
         <v>700</v>
-      </c>
-      <c r="K52" s="3">
-        <v>400</v>
       </c>
       <c r="L52" s="3">
         <v>400</v>
@@ -4402,44 +4521,44 @@
         <v>400</v>
       </c>
       <c r="O52" s="3">
+        <v>400</v>
+      </c>
+      <c r="P52" s="3">
         <v>4300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>5200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>5700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>6200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>6700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>7200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>7600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>8000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>8300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>8800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>9200</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4455,8 +4574,11 @@
       <c r="AF52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4547,83 +4669,86 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>62300</v>
+      </c>
+      <c r="E54" s="3">
         <v>74200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>79200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>86000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>102400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>111800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>125400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>140500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>150500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>169300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>193700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>213200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>243500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>270100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>299400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>333200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>355100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>390900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>439500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>465200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>328000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>358700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>378100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>392400</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4639,8 +4764,11 @@
       <c r="AF54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4673,8 +4801,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4707,83 +4836,84 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E57" s="3">
         <v>1000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>8200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>9100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>9400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>9000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>16400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>6200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>5300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>7200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2500</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4799,22 +4929,25 @@
       <c r="AF57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E58" s="3">
         <v>3500</v>
-      </c>
-      <c r="E58" s="3">
-        <v>3600</v>
       </c>
       <c r="F58" s="3">
         <v>3600</v>
       </c>
       <c r="G58" s="3">
-        <v>3700</v>
+        <v>3600</v>
       </c>
       <c r="H58" s="3">
         <v>3700</v>
@@ -4826,10 +4959,10 @@
         <v>3700</v>
       </c>
       <c r="K58" s="3">
+        <v>3700</v>
+      </c>
+      <c r="L58" s="3">
         <v>3400</v>
-      </c>
-      <c r="L58" s="3">
-        <v>3300</v>
       </c>
       <c r="M58" s="3">
         <v>3300</v>
@@ -4838,7 +4971,7 @@
         <v>3300</v>
       </c>
       <c r="O58" s="3">
-        <v>0</v>
+        <v>3300</v>
       </c>
       <c r="P58" s="3">
         <v>0</v>
@@ -4891,8 +5024,11 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4900,74 +5036,74 @@
         <v>13800</v>
       </c>
       <c r="E59" s="3">
+        <v>13800</v>
+      </c>
+      <c r="F59" s="3">
         <v>9700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>8700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>8200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>6000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2500</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L59" s="3">
         <v>2000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>14300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>17100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>18900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>18300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>20100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>13300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>14800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>13200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>15900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>15700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>6900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2700</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4983,83 +5119,86 @@
       <c r="AF59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>23100</v>
+      </c>
+      <c r="E60" s="3">
         <v>22200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>19800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>17800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>19400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>17000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>12400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>12800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>16300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>19800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>19900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>17200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>18400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>21600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>27100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>27500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>29500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>22300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>31200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>19500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>21200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>19100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>14100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>5200</v>
       </c>
-      <c r="AA60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5075,47 +5214,50 @@
       <c r="AF60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>20400</v>
+      </c>
+      <c r="E61" s="3">
         <v>20800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>21100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>21500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>21800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>22100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>22500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>22800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>22900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>23200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>23400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>23600</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -5167,8 +5309,11 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5202,48 +5347,48 @@
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N62" s="3">
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O62" s="3">
         <v>2000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>23800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>24000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>24200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>24400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>6900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>6500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>6000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>4200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>500</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5259,8 +5404,11 @@
       <c r="AF62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5351,8 +5499,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5443,8 +5594,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5535,83 +5689,86 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>43500</v>
+      </c>
+      <c r="E66" s="3">
         <v>43000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>40900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>39300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>41200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>39000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>34800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>35600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>39300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>43000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>43300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>42900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>42200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>45700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>51400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>51900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>36400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>28700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>37300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>23700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>23300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>19800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>14700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>5800</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5627,8 +5784,11 @@
       <c r="AF66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5661,8 +5821,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5753,8 +5914,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5845,8 +6009,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5937,8 +6104,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6029,83 +6199,86 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-704800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-691800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-684000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-674600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-659200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-646500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-627200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-611200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-594500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-577700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-550600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-526700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-492400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-465300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-438600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-399100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-356300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-305100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-258200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-209800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-170900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-132000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-103400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-76200</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6121,8 +6294,11 @@
       <c r="AF72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6213,8 +6389,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6305,8 +6484,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6397,83 +6579,86 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>18800</v>
+      </c>
+      <c r="E76" s="3">
         <v>31100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>38300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>46700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>61300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>72700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>90600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>104900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>111300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>126300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>150400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>170400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>201400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>224400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>248000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>281300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>318700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>362200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>402300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>441500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>304700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>338900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>363400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>386700</v>
       </c>
-      <c r="AA76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6489,8 +6674,11 @@
       <c r="AF76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6581,197 +6769,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AE80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AF80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-7700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-9400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-15400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-12700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-19300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-16000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-16700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-16800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-27100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-23900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-34300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-27100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-26700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-39500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-42800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-51200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-46900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-48400</v>
-      </c>
-      <c r="V81" s="3">
-        <v>-38900</v>
       </c>
       <c r="W81" s="3">
         <v>-38900</v>
       </c>
       <c r="X81" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="Y81" s="3">
         <v>-28500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-27200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-17600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-13200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-11400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-13400</v>
       </c>
-      <c r="AD81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6804,13 +7001,14 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="E83" s="3">
         <v>800</v>
@@ -6822,7 +7020,7 @@
         <v>800</v>
       </c>
       <c r="H83" s="3">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="I83" s="3">
         <v>1000</v>
@@ -6831,7 +7029,7 @@
         <v>1000</v>
       </c>
       <c r="K83" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="L83" s="3">
         <v>900</v>
@@ -6855,29 +7053,29 @@
         <v>900</v>
       </c>
       <c r="S83" s="3">
+        <v>900</v>
+      </c>
+      <c r="T83" s="3">
         <v>700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>500</v>
-      </c>
-      <c r="U83" s="3">
-        <v>200</v>
       </c>
       <c r="V83" s="3">
         <v>200</v>
       </c>
       <c r="W83" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="X83" s="3">
         <v>300</v>
       </c>
       <c r="Y83" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z83" s="3">
         <v>200</v>
       </c>
-      <c r="Z83" s="3">
-        <v>0</v>
-      </c>
       <c r="AA83" s="3">
         <v>0</v>
       </c>
@@ -6887,8 +7085,8 @@
       <c r="AC83" s="3">
         <v>0</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>3</v>
+      <c r="AD83" s="3">
+        <v>0</v>
       </c>
       <c r="AE83" s="3" t="s">
         <v>3</v>
@@ -6896,8 +7094,11 @@
       <c r="AF83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6988,8 +7189,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7080,8 +7284,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7172,8 +7379,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7264,8 +7474,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7356,100 +7569,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-4900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-6300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-13800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-8400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-7400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-13100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-18900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-19500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-19200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-17100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-22400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-24000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-23400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-26100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-44700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-30800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-41100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-24300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-30700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-29400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-17500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-11700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-21900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-17500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-11400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-10800</v>
       </c>
-      <c r="AD89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7482,8 +7701,9 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7496,32 +7716,32 @@
       <c r="F91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H91" s="3">
         <v>0</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>3</v>
+      <c r="I91" s="3">
+        <v>0</v>
       </c>
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
-        <v>-800</v>
+        <v>0</v>
       </c>
       <c r="P91" s="3">
         <v>-800</v>
@@ -7530,25 +7750,25 @@
         <v>-800</v>
       </c>
       <c r="R91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="S91" s="3">
         <v>-2200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-7300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-11500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-4000</v>
-      </c>
-      <c r="V91" s="3">
-        <v>-800</v>
       </c>
       <c r="W91" s="3">
         <v>-800</v>
       </c>
       <c r="X91" s="3">
-        <v>-100</v>
+        <v>-800</v>
       </c>
       <c r="Y91" s="3">
         <v>-100</v>
@@ -7557,25 +7777,28 @@
         <v>-100</v>
       </c>
       <c r="AA91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-100</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-200</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7666,8 +7889,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7758,8 +7984,11 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7767,91 +7996,94 @@
         <v>0</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>39600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>13700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>15000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>1000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>25300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>7600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>22500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>14000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>21200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>16000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>17300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-11600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-10300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-20400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-36500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-135400</v>
-      </c>
-      <c r="Y94" s="3">
-        <v>-100</v>
       </c>
       <c r="Z94" s="3">
         <v>-100</v>
       </c>
       <c r="AA94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="3">
         <v>-100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-700</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7884,8 +8116,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7922,8 +8155,8 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -7976,8 +8209,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8068,8 +8304,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8160,8 +8399,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8252,8 +8494,11 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8263,89 +8508,92 @@
       <c r="E100" s="3">
         <v>0</v>
       </c>
-      <c r="F100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
+      <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H100" s="3">
         <v>0</v>
       </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>8700</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
         <v>0</v>
       </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>100</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P100" s="3">
         <v>-600</v>
-      </c>
-      <c r="P100" s="3">
-        <v>-400</v>
       </c>
       <c r="Q100" s="3">
         <v>-400</v>
       </c>
       <c r="R100" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>500</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>165600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>400</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>229900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>109900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>46300</v>
       </c>
-      <c r="AD100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8382,8 +8630,8 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -8436,96 +8684,102 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-4900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-5700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>25800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>5300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>7500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-12000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>15100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-11900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>3300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-3100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-28000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-28600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-10500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-27400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-33900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-52600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-34100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>114500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-65600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-152900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-13400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>208000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-18300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>98400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>34900</v>
       </c>
-      <c r="AD102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PASG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PASG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="92">
   <si>
     <t>PASG</t>
   </si>
@@ -656,142 +656,146 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="33" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="34" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AF7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AG7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -831,8 +835,8 @@
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P8" s="3">
-        <v>0</v>
+      <c r="P8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q8" s="3">
         <v>0</v>
@@ -885,8 +889,11 @@
       <c r="AG8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -980,8 +987,11 @@
       <c r="AG9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1075,8 +1085,11 @@
       <c r="AG10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1110,103 +1123,107 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E12" s="3">
         <v>5400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>4300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>5800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>7700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>9600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>8700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>10400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>11500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>12200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>15100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>17300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>16800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>17700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>16900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>26800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>27700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>34000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>32100</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>33100</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>26500</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>28900</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>20800</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>19900</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>13100</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>10000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>10400</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>6800</v>
       </c>
-      <c r="AE12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1300,50 +1317,53 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
         <v>3500</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
         <v>2600</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>4800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>400</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>5400</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3">
         <v>11300</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1353,8 +1373,8 @@
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
@@ -1395,13 +1415,16 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
         <v>200</v>
@@ -1413,10 +1436,10 @@
         <v>200</v>
       </c>
       <c r="H15" s="3">
+        <v>200</v>
+      </c>
+      <c r="I15" s="3">
         <v>700</v>
-      </c>
-      <c r="I15" s="3">
-        <v>800</v>
       </c>
       <c r="J15" s="3">
         <v>800</v>
@@ -1428,7 +1451,7 @@
         <v>800</v>
       </c>
       <c r="M15" s="3">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="N15" s="3">
         <v>1000</v>
@@ -1437,7 +1460,7 @@
         <v>1000</v>
       </c>
       <c r="P15" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
@@ -1490,8 +1513,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1522,198 +1548,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E17" s="3">
         <v>10300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>8700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>10300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>13800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>14300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>15900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>16900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>18100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>18400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>23300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>25400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>24600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>28200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>27500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>39800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>42800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>51200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>47100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>48500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>38900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>39100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>28600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>27300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>17900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>13600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>11600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>7800</v>
       </c>
-      <c r="AE17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-10300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-8700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-10300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-13800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-14300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-15900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-16900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-18100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-18400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-23300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-25400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-24600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-28200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-27500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-39800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-42800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-51200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-47100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-48500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-38900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-39100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-28600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-27300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-17900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-13600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-11600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-7800</v>
       </c>
-      <c r="AE18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1747,67 +1780,68 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-400</v>
+        <v>-700</v>
       </c>
       <c r="E20" s="3">
         <v>-400</v>
       </c>
       <c r="F20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="G20" s="3">
         <v>500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-200</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>-200</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>300</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
         <v>0</v>
       </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>200</v>
-      </c>
-      <c r="V20" s="3">
-        <v>100</v>
       </c>
       <c r="W20" s="3">
         <v>100</v>
@@ -1822,123 +1856,129 @@
         <v>100</v>
       </c>
       <c r="AA20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB20" s="3">
         <v>300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-5700</v>
       </c>
-      <c r="AE20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-9800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-8100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-10600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-13300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-16300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-14900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-16000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-17200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-17500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-22400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-24400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-23200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-26100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-25800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-38600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-41900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-50500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-46500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-48200</v>
-      </c>
-      <c r="W21" s="3">
-        <v>-38700</v>
       </c>
       <c r="X21" s="3">
         <v>-38700</v>
       </c>
       <c r="Y21" s="3">
+        <v>-38700</v>
+      </c>
+      <c r="Z21" s="3">
         <v>-28300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-27000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-17500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-13100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-11300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-13400</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1978,8 +2018,8 @@
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -2032,103 +2072,109 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-13000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-7700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-9400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-15400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-12700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-19300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-16000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-16700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-16800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-27100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-23900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-34300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-27100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-26700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-39500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-42800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-51200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-46900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-48400</v>
-      </c>
-      <c r="W23" s="3">
-        <v>-38900</v>
       </c>
       <c r="X23" s="3">
         <v>-38900</v>
       </c>
       <c r="Y23" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="Z23" s="3">
         <v>-28500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-27200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-17600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-13200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-11400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-13400</v>
       </c>
-      <c r="AE23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2168,8 +2214,8 @@
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="P24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -2222,8 +2268,11 @@
       <c r="AG24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2317,198 +2366,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-13000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-7700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-9400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-15400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-12700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-19300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-16000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-16700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-16800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-27100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-23900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-34300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-27100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-26700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-39500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-42800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-51200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-46900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-48400</v>
-      </c>
-      <c r="W26" s="3">
-        <v>-38900</v>
       </c>
       <c r="X26" s="3">
         <v>-38900</v>
       </c>
       <c r="Y26" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="Z26" s="3">
         <v>-28500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-27200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-17600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-13200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-11400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-13400</v>
       </c>
-      <c r="AE26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-13000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-7700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-9400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-15400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-12700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-19300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-16000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-16700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-16800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-27100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-23900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-34300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-27100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-26700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-39500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-42800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-51200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-46900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-48400</v>
-      </c>
-      <c r="W27" s="3">
-        <v>-38900</v>
       </c>
       <c r="X27" s="3">
         <v>-38900</v>
       </c>
       <c r="Y27" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="Z27" s="3">
         <v>-28500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-27200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-17600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-13200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-11400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-13400</v>
       </c>
-      <c r="AE27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2602,8 +2660,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2697,8 +2758,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2792,8 +2856,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2887,67 +2954,70 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="E32" s="3">
         <v>400</v>
       </c>
       <c r="F32" s="3">
+        <v>400</v>
+      </c>
+      <c r="G32" s="3">
         <v>-500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>200</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>200</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-300</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
         <v>0</v>
       </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-200</v>
-      </c>
-      <c r="V32" s="3">
-        <v>-100</v>
       </c>
       <c r="W32" s="3">
         <v>-100</v>
@@ -2962,123 +3032,129 @@
         <v>-100</v>
       </c>
       <c r="AA32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AB32" s="3">
         <v>-300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>5700</v>
       </c>
-      <c r="AE32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-13000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-7700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-9400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-15400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-12700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-19300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-16000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-16700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-16800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-27100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-23900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-34300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-27100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-26700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-39500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-42800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-51200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-46900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-48400</v>
-      </c>
-      <c r="W33" s="3">
-        <v>-38900</v>
       </c>
       <c r="X33" s="3">
         <v>-38900</v>
       </c>
       <c r="Y33" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="Z33" s="3">
         <v>-28500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-27200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-17600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-13200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-11400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-13400</v>
       </c>
-      <c r="AE33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3172,203 +3248,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-13000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-7700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-9400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-15400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-12700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-19300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-16000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-16700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-16800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-27100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-23900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-34300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-27100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-26700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-39500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-42800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-51200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-46900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-48400</v>
-      </c>
-      <c r="W35" s="3">
-        <v>-38900</v>
       </c>
       <c r="X35" s="3">
         <v>-38900</v>
       </c>
       <c r="Y35" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="Z35" s="3">
         <v>-28500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-27200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-17600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-13200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-11400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-13400</v>
       </c>
-      <c r="AE35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AF38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AG38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3402,8 +3487,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3437,86 +3523,87 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>33300</v>
+      </c>
+      <c r="E41" s="3">
         <v>46300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>52800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>57600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>63400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>37600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>32300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>24800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>36800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>21700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>33600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>30300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>33400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>34600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>62600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>91100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>101600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>129000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>162900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>215500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>249500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>135000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>200600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>353400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>366800</v>
       </c>
-      <c r="AB41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3532,8 +3619,11 @@
       <c r="AG41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3550,62 +3640,62 @@
         <v>0</v>
       </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>39200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>52500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>67000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>67800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>92600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>99200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>121200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>134400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>155000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>151200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>148100</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>165500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>186800</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>191500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>192300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>188100</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>169800</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>135100</v>
       </c>
-      <c r="Z42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3621,14 +3711,17 @@
       <c r="AE42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AF42" s="3">
-        <v>0</v>
+      <c r="AF42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3665,12 +3758,12 @@
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O43" s="3">
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P43" s="3">
         <v>100</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
-      </c>
       <c r="Q43" s="3">
         <v>0</v>
       </c>
@@ -3722,8 +3815,11 @@
       <c r="AG43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3763,8 +3859,8 @@
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -3817,22 +3913,25 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>700</v>
+      </c>
+      <c r="E45" s="3">
         <v>800</v>
-      </c>
-      <c r="E45" s="3">
-        <v>1300</v>
       </c>
       <c r="F45" s="3">
         <v>1300</v>
       </c>
       <c r="G45" s="3">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="H45" s="3">
         <v>1200</v>
@@ -3841,62 +3940,62 @@
         <v>1200</v>
       </c>
       <c r="J45" s="3">
+        <v>1200</v>
+      </c>
+      <c r="K45" s="3">
         <v>1800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>7400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>8800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>11300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>15900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>9300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>12100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>11000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>13400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>12400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>13800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>14800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>15300</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3912,86 +4011,89 @@
       <c r="AG45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>34700</v>
+      </c>
+      <c r="E46" s="3">
         <v>47800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>55700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>60300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>66700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>78800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>87200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>95000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>108300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>118000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>135700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>153600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>171600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>197000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>222500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>250600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>283000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>325100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>366500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>418800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>450900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>317200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>349500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>368200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>382100</v>
       </c>
-      <c r="AB46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4007,8 +4109,11 @@
       <c r="AG46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4048,8 +4153,8 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -4102,85 +4207,88 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E48" s="3">
         <v>14300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>18200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>18600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>19100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>23100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>24100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>29900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>31600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>32200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>33100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>39600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>41200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>42200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>42800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>43600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>44500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>23800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>17800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>13500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>6600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>900</v>
-      </c>
-      <c r="Z48" s="3">
-        <v>1100</v>
       </c>
       <c r="AA48" s="3">
         <v>1100</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>3</v>
+      <c r="AB48" s="3">
+        <v>1100</v>
       </c>
       <c r="AC48" s="3" t="s">
         <v>3</v>
@@ -4197,8 +4305,11 @@
       <c r="AG48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4292,8 +4403,11 @@
       <c r="AG49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4387,8 +4501,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4482,8 +4599,11 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4491,7 +4611,7 @@
         <v>200</v>
       </c>
       <c r="E52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F52" s="3">
         <v>300</v>
@@ -4500,7 +4620,7 @@
         <v>300</v>
       </c>
       <c r="H52" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="I52" s="3">
         <v>500</v>
@@ -4509,10 +4629,10 @@
         <v>500</v>
       </c>
       <c r="K52" s="3">
+        <v>500</v>
+      </c>
+      <c r="L52" s="3">
         <v>700</v>
-      </c>
-      <c r="L52" s="3">
-        <v>400</v>
       </c>
       <c r="M52" s="3">
         <v>400</v>
@@ -4524,44 +4644,44 @@
         <v>400</v>
       </c>
       <c r="P52" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q52" s="3">
         <v>4300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>5200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>5700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>6200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>6700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>7200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>7600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>8000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>8300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>8800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>9200</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4577,8 +4697,11 @@
       <c r="AG52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4672,86 +4795,89 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>36500</v>
+      </c>
+      <c r="E54" s="3">
         <v>62300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>74200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>79200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>86000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>102400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>111800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>125400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>140500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>150500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>169300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>193700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>213200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>243500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>270100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>299400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>333200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>355100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>390900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>439500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>465200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>328000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>358700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>378100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>392400</v>
       </c>
-      <c r="AB54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4767,8 +4893,11 @@
       <c r="AG54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4802,8 +4931,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4837,86 +4967,87 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E57" s="3">
         <v>1100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>8200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>9100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>9400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>9000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>16400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>6200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>5300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>3400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>7200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2500</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4932,25 +5063,28 @@
       <c r="AG57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E58" s="3">
         <v>3600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3500</v>
-      </c>
-      <c r="F58" s="3">
-        <v>3600</v>
       </c>
       <c r="G58" s="3">
         <v>3600</v>
       </c>
       <c r="H58" s="3">
-        <v>3700</v>
+        <v>3600</v>
       </c>
       <c r="I58" s="3">
         <v>3700</v>
@@ -4962,10 +5096,10 @@
         <v>3700</v>
       </c>
       <c r="L58" s="3">
+        <v>3700</v>
+      </c>
+      <c r="M58" s="3">
         <v>3400</v>
-      </c>
-      <c r="M58" s="3">
-        <v>3300</v>
       </c>
       <c r="N58" s="3">
         <v>3300</v>
@@ -4974,7 +5108,7 @@
         <v>3300</v>
       </c>
       <c r="P58" s="3">
-        <v>0</v>
+        <v>3300</v>
       </c>
       <c r="Q58" s="3">
         <v>0</v>
@@ -5027,8 +5161,11 @@
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5039,74 +5176,74 @@
         <v>13800</v>
       </c>
       <c r="F59" s="3">
+        <v>13800</v>
+      </c>
+      <c r="G59" s="3">
         <v>9700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>8700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>8200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>6000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2500</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3">
         <v>2000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>14300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>17100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>18900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>18300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>20100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>13300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>14800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>13200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>15900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>15700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>6900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2700</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5122,86 +5259,89 @@
       <c r="AG59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>20100</v>
+      </c>
+      <c r="E60" s="3">
         <v>23100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>22200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>19800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>17800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>19400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>17000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>12400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>12800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>16300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>19800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>19900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>17200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>18400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>21600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>27100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>27500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>29500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>22300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>31200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>19500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>21200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>19100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>14100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>5200</v>
       </c>
-      <c r="AB60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5217,50 +5357,53 @@
       <c r="AG60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E61" s="3">
         <v>20400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>20800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>21100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>21500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>21800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>22100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>22500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>22800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>22900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>23200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>23400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>23600</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -5312,8 +5455,11 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5350,48 +5496,48 @@
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O62" s="3">
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P62" s="3">
         <v>2000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>23800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>24000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>24200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>24400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>6900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>6500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>6000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>4200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>500</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5407,8 +5553,11 @@
       <c r="AG62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5502,8 +5651,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5597,8 +5749,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5692,86 +5847,89 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>24700</v>
+      </c>
+      <c r="E66" s="3">
         <v>43500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>43000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>40900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>39300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>41200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>39000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>34800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>35600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>39300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>43000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>43300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>42900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>42200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>45700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>51400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>51900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>36400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>28700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>37300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>23700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>23300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>19800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>14700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>5800</v>
       </c>
-      <c r="AB66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5787,8 +5945,11 @@
       <c r="AG66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5822,8 +5983,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5917,8 +6079,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6012,8 +6177,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6107,8 +6275,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6202,86 +6373,89 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-712300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-704800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-691800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-684000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-674600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-659200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-646500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-627200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-611200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-594500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-577700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-550600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-526700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-492400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-465300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-438600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-399100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-356300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-305100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-258200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-209800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-170900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-132000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-103400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-76200</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6297,8 +6471,11 @@
       <c r="AG72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6392,8 +6569,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6487,8 +6667,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6582,86 +6765,89 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E76" s="3">
         <v>18800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>31100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>38300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>46700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>61300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>72700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>90600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>104900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>111300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>126300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>150400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>170400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>201400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>224400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>248000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>281300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>318700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>362200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>402300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>441500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>304700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>338900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>363400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>386700</v>
       </c>
-      <c r="AB76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6677,8 +6863,11 @@
       <c r="AG76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6772,203 +6961,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AF80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AG80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-13000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-7700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-9400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-15400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-12700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-19300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-16000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-16700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-16800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-27100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-23900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-34300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-27100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-26700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-39500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-42800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-51200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-46900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-48400</v>
-      </c>
-      <c r="W81" s="3">
-        <v>-38900</v>
       </c>
       <c r="X81" s="3">
         <v>-38900</v>
       </c>
       <c r="Y81" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="Z81" s="3">
         <v>-28500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-27200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-17600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-13200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-11400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-13400</v>
       </c>
-      <c r="AE81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7002,16 +7200,17 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>200</v>
+      </c>
+      <c r="E83" s="3">
         <v>700</v>
-      </c>
-      <c r="E83" s="3">
-        <v>800</v>
       </c>
       <c r="F83" s="3">
         <v>800</v>
@@ -7023,7 +7222,7 @@
         <v>800</v>
       </c>
       <c r="I83" s="3">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="J83" s="3">
         <v>1000</v>
@@ -7032,7 +7231,7 @@
         <v>1000</v>
       </c>
       <c r="L83" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="M83" s="3">
         <v>900</v>
@@ -7056,29 +7255,29 @@
         <v>900</v>
       </c>
       <c r="T83" s="3">
+        <v>900</v>
+      </c>
+      <c r="U83" s="3">
         <v>700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>500</v>
-      </c>
-      <c r="V83" s="3">
-        <v>200</v>
       </c>
       <c r="W83" s="3">
         <v>200</v>
       </c>
       <c r="X83" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Y83" s="3">
         <v>300</v>
       </c>
       <c r="Z83" s="3">
+        <v>300</v>
+      </c>
+      <c r="AA83" s="3">
         <v>200</v>
       </c>
-      <c r="AA83" s="3">
-        <v>0</v>
-      </c>
       <c r="AB83" s="3">
         <v>0</v>
       </c>
@@ -7088,8 +7287,8 @@
       <c r="AD83" s="3">
         <v>0</v>
       </c>
-      <c r="AE83" s="3" t="s">
-        <v>3</v>
+      <c r="AE83" s="3">
+        <v>0</v>
       </c>
       <c r="AF83" s="3" t="s">
         <v>3</v>
@@ -7097,8 +7296,11 @@
       <c r="AG83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7192,8 +7394,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7287,8 +7492,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7382,8 +7590,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7477,8 +7688,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7572,103 +7786,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-6500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-4900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-6300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-13800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-8400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-7400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-13100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-18900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-19500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-19200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-17100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-22400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-24000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-23400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-26100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-44700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-30800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-41100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-24300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-30700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-29400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-17500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-11700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-21900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-17500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-11400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-10800</v>
       </c>
-      <c r="AE89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7702,8 +7922,9 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7719,32 +7940,32 @@
       <c r="G91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I91" s="3">
         <v>0</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>3</v>
+      <c r="J91" s="3">
+        <v>0</v>
       </c>
       <c r="K91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
-        <v>-800</v>
+        <v>0</v>
       </c>
       <c r="Q91" s="3">
         <v>-800</v>
@@ -7753,25 +7974,25 @@
         <v>-800</v>
       </c>
       <c r="S91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="T91" s="3">
         <v>-2200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-7300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-11500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-4000</v>
-      </c>
-      <c r="W91" s="3">
-        <v>-800</v>
       </c>
       <c r="X91" s="3">
         <v>-800</v>
       </c>
       <c r="Y91" s="3">
-        <v>-100</v>
+        <v>-800</v>
       </c>
       <c r="Z91" s="3">
         <v>-100</v>
@@ -7780,25 +8001,28 @@
         <v>-100</v>
       </c>
       <c r="AB91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-200</v>
       </c>
-      <c r="AE91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7892,8 +8116,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7987,8 +8214,11 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7999,91 +8229,94 @@
         <v>0</v>
       </c>
       <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
         <v>600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>39600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>13700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>15000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>1000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>25300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>7600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>22500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>14000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>21200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-4800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>16000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>17300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-11600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-10300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-20400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-36500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-135400</v>
-      </c>
-      <c r="Z94" s="3">
-        <v>-100</v>
       </c>
       <c r="AA94" s="3">
         <v>-100</v>
       </c>
       <c r="AB94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="3">
         <v>-100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-700</v>
       </c>
-      <c r="AE94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8117,8 +8350,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8158,8 +8392,8 @@
       <c r="O96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -8212,8 +8446,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8307,8 +8544,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8402,8 +8642,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8497,13 +8740,16 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
+      <c r="D100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E100" s="3">
         <v>0</v>
@@ -8511,89 +8757,92 @@
       <c r="F100" s="3">
         <v>0</v>
       </c>
-      <c r="G100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
+      <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I100" s="3">
         <v>0</v>
       </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>8700</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
         <v>0</v>
       </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>100</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P100" s="3">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-600</v>
-      </c>
-      <c r="Q100" s="3">
-        <v>-400</v>
       </c>
       <c r="R100" s="3">
         <v>-400</v>
       </c>
       <c r="S100" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>500</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>165600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>400</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
       <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
         <v>-1600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>229900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>109900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>46300</v>
       </c>
-      <c r="AE100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8633,8 +8882,8 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -8687,99 +8936,105 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-6500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-4900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-5700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>25800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>5300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>7500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-12000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>15100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-11900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>3300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-3100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-28000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-28600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-10500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-27400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-33900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-52600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-34100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>114500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-65600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-152900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-13400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>208000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-18300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>98400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>34900</v>
       </c>
-      <c r="AE102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
